--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_E7D48C030F9A8C95E06B48120F88209764BF9059" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6E52DF1-81C7-4978-B2A6-1604C057AB67}"/>
+  <bookViews>
+    <workbookView xWindow="-25155" yWindow="3540" windowWidth="31020" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Weapon_Master" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Armor_Master" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Item_Master" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Option_Master" sheetId="4" r:id="rId7"/>
+    <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
+    <sheet name="Armor_Master" sheetId="2" r:id="rId2"/>
+    <sheet name="Item_Master" sheetId="3" r:id="rId3"/>
+    <sheet name="Option_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="2XdxoDNmepd5wUdrOjM5AYD2fl/0TNPY3WAwExGsGHM="/>
@@ -19,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -72,9 +81,6 @@
     <t>철검</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
     <t>Option_001</t>
   </si>
   <si>
@@ -184,29 +190,75 @@
   </si>
   <si>
     <t>Effect_Penetration</t>
+  </si>
+  <si>
+    <t>Armor_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철갑옷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간 포션</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,11 +266,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -232,51 +290,41 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -466,35 +514,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.57"/>
-    <col customWidth="1" min="2" max="2" width="15.43"/>
-    <col customWidth="1" min="3" max="3" width="14.43"/>
-    <col customWidth="1" min="4" max="4" width="14.57"/>
-    <col customWidth="1" min="5" max="5" width="12.14"/>
-    <col customWidth="1" min="6" max="6" width="12.43"/>
-    <col customWidth="1" min="7" max="7" width="12.0"/>
-    <col customWidth="1" min="8" max="8" width="13.43"/>
-    <col customWidth="1" min="9" max="9" width="12.0"/>
-    <col customWidth="1" min="10" max="10" width="12.86"/>
-    <col customWidth="1" min="11" max="11" width="12.71"/>
-    <col customWidth="1" min="12" max="12" width="15.14"/>
-    <col customWidth="1" min="13" max="13" width="12.71"/>
-    <col customWidth="1" min="14" max="14" width="15.14"/>
-    <col customWidth="1" min="15" max="15" width="36.57"/>
-    <col customWidth="1" min="16" max="26" width="8.71"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="36.5703125" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:15" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1">
+    <row r="2" spans="1:15" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -552,148 +600,146 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F2" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G2" s="3" t="s">
+        <v>1.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2">
+        <v>15</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2">
+        <v>20</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="O2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="E3" s="2">
-        <v>0.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>17</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="2">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2">
+        <v>5</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="O3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:15" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>60.0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>60</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0.2</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>17</v>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="2">
+        <v>5</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1"/>
-    <row r="6" ht="16.5" customHeight="1"/>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="8" ht="16.5" customHeight="1"/>
-    <row r="9" ht="16.5" customHeight="1"/>
-    <row r="10" ht="16.5" customHeight="1"/>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
+    <row r="5" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="6" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="8" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -1679,90 +1725,112 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.57"/>
-    <col customWidth="1" min="2" max="2" width="14.71"/>
-    <col customWidth="1" min="3" max="3" width="12.14"/>
-    <col customWidth="1" min="4" max="4" width="11.29"/>
-    <col customWidth="1" min="5" max="5" width="16.43"/>
-    <col customWidth="1" min="6" max="6" width="15.57"/>
-    <col customWidth="1" min="7" max="7" width="16.43"/>
-    <col customWidth="1" min="8" max="8" width="15.57"/>
-    <col customWidth="1" min="9" max="26" width="8.71"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" customWidth="1"/>
+    <col min="9" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1"/>
-    <row r="3" ht="16.5" customHeight="1"/>
-    <row r="4" ht="16.5" customHeight="1"/>
-    <row r="5" ht="16.5" customHeight="1"/>
-    <row r="6" ht="16.5" customHeight="1"/>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="8" ht="16.5" customHeight="1"/>
-    <row r="9" ht="16.5" customHeight="1"/>
-    <row r="10" ht="16.5" customHeight="1"/>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
+    <row r="2" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="4" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="5" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="6" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="8" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -2748,82 +2816,98 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.71"/>
-    <col customWidth="1" min="2" max="2" width="12.43"/>
-    <col customWidth="1" min="3" max="5" width="14.29"/>
-    <col customWidth="1" min="6" max="6" width="15.14"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
+      <c r="F1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1"/>
-    <row r="3" ht="16.5" customHeight="1"/>
-    <row r="4" ht="16.5" customHeight="1"/>
-    <row r="5" ht="16.5" customHeight="1"/>
-    <row r="6" ht="16.5" customHeight="1"/>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="8" ht="16.5" customHeight="1"/>
-    <row r="9" ht="16.5" customHeight="1"/>
-    <row r="10" ht="16.5" customHeight="1"/>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
+    <row r="2" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="4" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="5" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="6" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="8" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -3809,104 +3893,101 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.43"/>
-    <col customWidth="1" min="2" max="2" width="19.43"/>
-    <col customWidth="1" min="3" max="3" width="17.71"/>
-    <col customWidth="1" min="4" max="4" width="14.29"/>
-    <col customWidth="1" min="5" max="26" width="8.71"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1">
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>46</v>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>48</v>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="8" ht="16.5" customHeight="1"/>
-    <row r="9" ht="16.5" customHeight="1"/>
-    <row r="10" ht="16.5" customHeight="1"/>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="8" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:4" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -4892,9 +4973,8 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_E7D48C030F9A8C95E06B48120F88209764BF9059" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6E52DF1-81C7-4978-B2A6-1604C057AB67}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_E7D48C030F9A8C95E06B48120F88209764BF9059" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7976F5BF-664B-4650-8DA9-3410F06A33C2}"/>
   <bookViews>
-    <workbookView xWindow="-25155" yWindow="3540" windowWidth="31020" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29700" yWindow="2820" windowWidth="31020" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -218,6 +218,16 @@
   <si>
     <t>Option_005</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Description</t>
+  </si>
+  <si>
+    <t>아이템 설명입니다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Price</t>
   </si>
 </sst>
 </file>
@@ -2831,7 +2841,9 @@
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="5" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="26" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
@@ -2853,8 +2865,12 @@
       <c r="F1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="G1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2892,6 +2908,12 @@
       </c>
       <c r="F2">
         <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d690ad99c43bdc4/문서/GitHub/Adventure/JsonFile/Assets/ExcelFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_E7D48C030F9A8C95E06B48120F88209764BF9059" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7976F5BF-664B-4650-8DA9-3410F06A33C2}"/>
   <bookViews>
-    <workbookView xWindow="-29700" yWindow="2820" windowWidth="31020" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29700" yWindow="2820" windowWidth="31020" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -233,7 +232,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -530,20 +529,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.7109375" customWidth="1"/>
     <col min="12" max="12" width="15.140625" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
@@ -716,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -1742,7 +1741,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2833,7 +2832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3922,7 +3921,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A9C86A-5FE7-4F75-85A7-89758C023AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29700" yWindow="2820" windowWidth="31020" windowHeight="11295"/>
+    <workbookView xWindow="10200" yWindow="4470" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -227,13 +228,25 @@
   </si>
   <si>
     <t>Item_Price</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>One-Handed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +282,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,7 +298,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -301,11 +321,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -315,6 +346,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -529,8 +564,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -548,10 +583,12 @@
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
     <col min="14" max="14" width="15.140625" customWidth="1"/>
     <col min="15" max="15" width="36.5703125" customWidth="1"/>
-    <col min="16" max="26" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,8 +634,14 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -644,8 +687,14 @@
       <c r="O2" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" ht="16.5" customHeight="1">
+    <row r="3" spans="1:17" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -691,8 +740,14 @@
       <c r="O3" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="P3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="16.5" customHeight="1">
+    <row r="4" spans="1:17" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -736,19 +791,25 @@
       <c r="O4" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="P4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="6" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:15" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:15" ht="16.5" customHeight="1"/>
+    <row r="5" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="6" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="8" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:17" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -1736,12 +1797,12 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2832,7 +2893,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3921,7 +3982,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A9C86A-5FE7-4F75-85A7-89758C023AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10200" yWindow="4470" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10200" yWindow="4470" windowWidth="34995" windowHeight="15345"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Item_Master" sheetId="3" r:id="rId3"/>
     <sheet name="Option_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="2XdxoDNmepd5wUdrOjM5AYD2fl/0TNPY3WAwExGsGHM="/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -36,9 +35,6 @@
     <t>Weapon_Name</t>
   </si>
   <si>
-    <t>Weapon_Type</t>
-  </si>
-  <si>
     <t>Weapon_DMG</t>
   </si>
   <si>
@@ -106,9 +102,6 @@
   </si>
   <si>
     <t>Weapon_003</t>
-  </si>
-  <si>
-    <t>마법 지팡이</t>
   </si>
   <si>
     <t>Option_004</t>
@@ -239,14 +232,30 @@
   </si>
   <si>
     <t>One-Handed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>튼튼한 철로 만든 철 갑옷이다 사용자의 몸을 든든하게 지켜준다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>떡갈나무 지팡이</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +297,14 @@
       <name val="Noto Sans KR"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -336,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -350,6 +367,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -564,31 +583,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="36.5703125" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1">
+    <row r="1" spans="1:16" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,34 +650,31 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="b">
-        <v>1</v>
+      <c r="C2" s="2">
+        <v>100</v>
       </c>
       <c r="D2" s="2">
-        <v>100</v>
+        <v>1.2</v>
       </c>
       <c r="E2" s="2">
         <v>1.2</v>
       </c>
       <c r="F2" s="2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -669,49 +685,46 @@
       <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="2">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2">
-        <v>15</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="2">
+        <v>20</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="b">
-        <v>1</v>
+      <c r="C3" s="2">
+        <v>150</v>
       </c>
       <c r="D3" s="2">
-        <v>150</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E3" s="2">
         <v>1.1000000000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -722,43 +735,40 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="2">
+        <v>10</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="2">
+        <v>5</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="2">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2">
         <v>0</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2">
-        <v>10</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="2">
-        <v>5</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>60</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -767,49 +777,50 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="2">
         <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1.2</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="2">
-        <v>5</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2">
+      <c r="N4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="6" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:17" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:17" ht="16.5" customHeight="1"/>
+    <row r="5" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -1802,48 +1813,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
@@ -1863,10 +1880,10 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1875,21 +1892,34 @@
         <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
       </c>
+      <c r="I2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="5" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:26" ht="16.5" customHeight="1">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:26" ht="16.5" customHeight="1">
+      <c r="I5" s="2"/>
+    </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="7" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="8" spans="1:26" ht="16.5" customHeight="1"/>
@@ -2888,19 +2918,21 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="26" width="8.7109375" customWidth="1"/>
@@ -2908,28 +2940,28 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="G1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2952,25 +2984,25 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -3982,7 +4014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3995,69 +4027,69 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>Option_003</t>
-  </si>
-  <si>
-    <t>기본 철로 만든 검</t>
   </si>
   <si>
     <t>Weapon_002</t>
@@ -248,6 +245,1571 @@
   </si>
   <si>
     <t>떡갈나무 지팡이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>오목나무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지팡이</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>중급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>마법사들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>유용하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사용하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지팡이</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_005</t>
+  </si>
+  <si>
+    <t>Weapon_006</t>
+  </si>
+  <si>
+    <t>Weapon_007</t>
+  </si>
+  <si>
+    <t>Weapon_008</t>
+  </si>
+  <si>
+    <t>철 단검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>철로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>검</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>철로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>단검이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이곳저곳에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>유용하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사용이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>된다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>롱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>소드</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>강철로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>튼튼한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>검이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>짧지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>강력한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>위력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>활이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이동하면서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>쏘기에도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>유용하다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>롱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보우</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>숏 보우</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사용하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>까다롭지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>강력한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>위력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>활이다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_009</t>
+  </si>
+  <si>
+    <t>Weapon_010</t>
+  </si>
+  <si>
+    <t>Weapon_011</t>
+  </si>
+  <si>
+    <t>Weapon_012</t>
+  </si>
+  <si>
+    <t>Weapon_013</t>
+  </si>
+  <si>
+    <t>Weapon_014</t>
+  </si>
+  <si>
+    <t>Weapon_015</t>
+  </si>
+  <si>
+    <r>
+      <t>가죽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>건틀릿</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가죽으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>건틀릿이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>적에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>휘두를때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>안전을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보장해주며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>꽤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>강한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일격을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>날릴수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>도와준다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>스파이크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>건틀릿</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>더욱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>튼튼한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가죽으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>장갑에다가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>강철로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>징을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>박아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>매우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>위협적인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>건틀릿이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>탄생했다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>츠바이 헨더</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>손잡이에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>검날까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>곧게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>뻗어있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>아주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>길고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>무거운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>검</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -353,7 +1915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -369,6 +1931,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -651,10 +2214,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
@@ -697,11 +2260,11 @@
       <c r="M2" s="2">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>18</v>
+      <c r="N2" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -709,10 +2272,10 @@
     </row>
     <row r="3" spans="1:16" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C3" s="2">
         <v>150</v>
@@ -736,22 +2299,22 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K3" s="2">
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="2">
         <v>5</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -759,10 +2322,10 @@
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2">
         <v>60</v>
@@ -786,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2">
         <v>5</v>
@@ -796,10 +2359,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -807,20 +2370,328 @@
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="8">
+        <v>80</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:16" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:16" ht="16.5" customHeight="1"/>
+    <row r="6" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="8">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="8">
+        <v>120</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="8">
+        <v>60</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="8">
+        <v>120</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="8">
+        <v>60</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="8">
+        <v>120</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="8">
+        <v>180</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A13" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -1832,34 +3703,34 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -1880,10 +3751,10 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1892,22 +3763,22 @@
         <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
@@ -2940,28 +4811,28 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -2984,25 +4855,25 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -4027,13 +5898,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="D1" s="1"/>
     </row>
@@ -4042,21 +5913,21 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
@@ -4064,32 +5935,32 @@
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="10200" yWindow="4470" windowWidth="34995" windowHeight="15345"/>
+    <workbookView xWindow="10200" yWindow="4470" windowWidth="34995" windowHeight="15345" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>Option_ID</t>
   </si>
   <si>
-    <t>Option_Description</t>
-  </si>
-  <si>
     <t>Effect_ID</t>
   </si>
   <si>
@@ -1810,6 +1807,10 @@
       </rPr>
       <t>.</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_Description</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2163,7 +2164,7 @@
     <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="113" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -2214,10 +2215,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
@@ -2261,10 +2262,10 @@
         <v>20</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -2314,7 +2315,7 @@
         <v>22</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -2325,7 +2326,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2">
         <v>60</v>
@@ -2362,7 +2363,7 @@
         <v>25</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -2370,10 +2371,10 @@
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="8">
         <v>80</v>
@@ -2403,15 +2404,15 @@
         <v>0</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" s="8">
         <v>30</v>
@@ -2441,15 +2442,15 @@
         <v>0</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="8">
         <v>120</v>
@@ -2479,15 +2480,15 @@
         <v>0</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="8">
         <v>60</v>
@@ -2517,15 +2518,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="8">
         <v>120</v>
@@ -2555,15 +2556,15 @@
         <v>0</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="8">
         <v>60</v>
@@ -2593,15 +2594,15 @@
         <v>0</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="8">
         <v>120</v>
@@ -2631,15 +2632,15 @@
         <v>0</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="8">
         <v>180</v>
@@ -2669,27 +2670,27 @@
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1"/>
@@ -3730,7 +3731,7 @@
         <v>13</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -3751,10 +3752,10 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -3763,22 +3764,22 @@
         <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
@@ -4829,10 +4830,10 @@
         <v>33</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -4855,25 +4856,25 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -5889,9 +5890,9 @@
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -5901,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D1" s="1"/>
     </row>
@@ -5913,10 +5914,10 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
@@ -5924,10 +5925,10 @@
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
@@ -5935,10 +5936,10 @@
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
@@ -5946,10 +5947,10 @@
         <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
@@ -5957,10 +5958,10 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61679B43-BC1C-4E87-A644-2CFD958C43CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10200" yWindow="4470" windowWidth="34995" windowHeight="15345" activeTab="3"/>
+    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -74,39 +75,12 @@
     <t>Weapon_001</t>
   </si>
   <si>
-    <t>철검</t>
-  </si>
-  <si>
-    <t>Option_001</t>
-  </si>
-  <si>
-    <t>Option_003</t>
-  </si>
-  <si>
     <t>Weapon_002</t>
   </si>
   <si>
-    <t>붉은 용의 검</t>
-  </si>
-  <si>
-    <t>Option_002</t>
-  </si>
-  <si>
-    <t>Option_005</t>
-  </si>
-  <si>
-    <t>붉은 용의 비늘로 제작된 검</t>
-  </si>
-  <si>
     <t>Weapon_003</t>
   </si>
   <si>
-    <t>Option_004</t>
-  </si>
-  <si>
-    <t>초보 마법사가 사용하기 적합한 지팡이</t>
-  </si>
-  <si>
     <t>Armor_ID</t>
   </si>
   <si>
@@ -147,36 +121,6 @@
   </si>
   <si>
     <t>Effect_ID</t>
-  </si>
-  <si>
-    <t>출혈 확률</t>
-  </si>
-  <si>
-    <t>Effect_Bleed</t>
-  </si>
-  <si>
-    <t>화염 속성 피해</t>
-  </si>
-  <si>
-    <t>Effect_Fire</t>
-  </si>
-  <si>
-    <t>크리티컬 확률 증가</t>
-  </si>
-  <si>
-    <t>Effect_Critical</t>
-  </si>
-  <si>
-    <t>마법 공격력 증가</t>
-  </si>
-  <si>
-    <t>Effect_MagicBoost</t>
-  </si>
-  <si>
-    <t>방어 무시</t>
-  </si>
-  <si>
-    <t>Effect_Penetration</t>
   </si>
   <si>
     <t>Armor_001</t>
@@ -241,135 +185,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>떡갈나무 지팡이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>오목나무</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>지팡이</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>중급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>마법사들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>유용하게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사용하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>지팡이</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Weapon_005</t>
   </si>
   <si>
@@ -380,10 +195,6 @@
   </si>
   <si>
     <t>Weapon_008</t>
-  </si>
-  <si>
-    <t>철 단검</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -442,1383 +253,52 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>철로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>만든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>단검이다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이곳저곳에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>유용하게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사용이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>된다</t>
-    </r>
+    <t>Weapon_009</t>
+  </si>
+  <si>
+    <t>Weapon_010</t>
+  </si>
+  <si>
+    <t>Weapon_011</t>
+  </si>
+  <si>
+    <t>Weapon_012</t>
+  </si>
+  <si>
+    <t>Weapon_013</t>
+  </si>
+  <si>
+    <t>Weapon_014</t>
+  </si>
+  <si>
+    <t>Weapon_015</t>
+  </si>
+  <si>
+    <t>Option_Description</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>롱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>소드</t>
-    </r>
+    <t>낡은 검</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>강철로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>만든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>튼튼한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>검이다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <t>나무 활</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>짧지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>강력한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>위력을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>가진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>활이다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이동하면서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>쏘기에도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>유용하다</t>
-    </r>
+    <t>낡은 단검</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>롱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>보우</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>숏 보우</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>사용하기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>까다롭지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>강력한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>위력을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>가진</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>활이다</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_009</t>
-  </si>
-  <si>
-    <t>Weapon_010</t>
-  </si>
-  <si>
-    <t>Weapon_011</t>
-  </si>
-  <si>
-    <t>Weapon_012</t>
-  </si>
-  <si>
-    <t>Weapon_013</t>
-  </si>
-  <si>
-    <t>Weapon_014</t>
-  </si>
-  <si>
-    <t>Weapon_015</t>
-  </si>
-  <si>
-    <r>
-      <t>가죽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>건틀릿</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>가죽으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>만든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>건틀릿이다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>적에게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>주먹을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>휘두를때</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>안전을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>보장해주며</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>꽤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>강한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일격을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>날릴수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>있게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>도와준다</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>스파이크</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>건틀릿</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>더욱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>튼튼한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>가죽으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>만든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>장갑에다가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>강철로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>만든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>징을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>박아</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>매우</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>위협적인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>건틀릿이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>탄생했다</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>츠바이 헨더</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>손잡이에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>검날까지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>곧게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>뻗어있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>아주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>길고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>무거운</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>검</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_Description</t>
+    <t>낡은 지팡이</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1868,6 +348,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1926,13 +413,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2147,7 +634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2215,27 +702,27 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
+      <c r="B2" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="C2" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2">
         <v>1.2</v>
       </c>
       <c r="E2" s="2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -2249,23 +736,15 @@
       <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="2">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="2">
-        <v>20</v>
-      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
       <c r="N2" s="7" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -2273,19 +752,19 @@
     </row>
     <row r="3" spans="1:16" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="C3" s="2">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2">
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -2299,23 +778,13 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="2">
-        <v>10</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="2">
-        <v>5</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -2323,25 +792,25 @@
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>66</v>
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="C4" s="2">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -2349,348 +818,180 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="2">
-        <v>5</v>
-      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="8">
-        <v>80</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="9">
+        <v>10</v>
+      </c>
+      <c r="D5" s="9">
         <v>0</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="2">
         <v>0</v>
       </c>
-      <c r="F5" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="F5" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="G5" s="9">
         <v>0</v>
       </c>
-      <c r="I5" s="8">
+      <c r="H5" s="9">
         <v>0</v>
       </c>
-      <c r="K5" s="8">
+      <c r="I5" s="9">
         <v>0</v>
       </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>68</v>
+      <c r="K5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="8">
-        <v>30</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>75</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="8">
-        <v>120</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>77</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="8">
-        <v>60</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>78</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="8">
-        <v>120</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>81</v>
-      </c>
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="8">
-        <v>60</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8">
-        <v>0</v>
-      </c>
-      <c r="N10" s="8" t="s">
-        <v>90</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="8">
-        <v>120</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.8</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>92</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="8">
-        <v>180</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1.6</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0</v>
-      </c>
-      <c r="I12" s="8">
-        <v>0</v>
-      </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>94</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>85</v>
+      <c r="A13" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1"/>
@@ -3685,7 +1986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3704,34 +2005,34 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -3752,10 +2053,10 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -3764,22 +2065,22 @@
         <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
@@ -4795,7 +3096,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4812,28 +3113,28 @@
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -4856,25 +3157,25 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -5886,7 +4187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -5899,70 +4200,40 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1"/>
     <row r="8" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61679B43-BC1C-4E87-A644-2CFD958C43CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -293,11 +292,27 @@
     <t>낡은 지팡이</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>Option_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 공격력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -634,7 +649,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -736,10 +751,18 @@
       <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
       <c r="N2" s="7" t="s">
         <v>51</v>
       </c>
@@ -778,10 +801,18 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
         <v>42</v>
@@ -818,10 +849,18 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
         <v>42</v>
@@ -855,8 +894,18 @@
       <c r="I5" s="9">
         <v>0</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="M5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
         <v>42</v>
@@ -875,6 +924,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
@@ -1986,7 +2036,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3096,7 +3146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4187,7 +4237,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4211,9 +4261,15 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580"/>
+    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -293,19 +293,68 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Option_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>추가 공격력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>null</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Effect_001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>null</t>
+    <t>Effect_002</t>
+  </si>
+  <si>
+    <t>크리티컬 확률 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor_002</t>
+  </si>
+  <si>
+    <t>가죽 갑옷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ull</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단단한 가죽으로 만든 갑옷이다. 사용자의 몸을 지켜준다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Option_002</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -752,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
@@ -802,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
@@ -850,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
@@ -895,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
@@ -2134,7 +2183,36 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
-      <c r="J3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
       <c r="I4" s="2"/>
@@ -4258,23 +4336,37 @@
       <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2"/>
@@ -5288,6 +5380,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" activeTab="3"/>
+    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="84">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -355,6 +355,53 @@
   </si>
   <si>
     <t>Option_002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor_003</t>
+  </si>
+  <si>
+    <t>천 갑옷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ull</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ull</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>천으로 만든 갑옷이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2215,8 +2262,36 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
       <c r="I5" s="2"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" activeTab="1"/>
+    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -126,10 +126,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>철갑옷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Option_001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -185,15 +181,6 @@
   </si>
   <si>
     <t>Weapon_005</t>
-  </si>
-  <si>
-    <t>Weapon_006</t>
-  </si>
-  <si>
-    <t>Weapon_007</t>
-  </si>
-  <si>
-    <t>Weapon_008</t>
   </si>
   <si>
     <r>
@@ -252,27 +239,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_009</t>
-  </si>
-  <si>
-    <t>Weapon_010</t>
-  </si>
-  <si>
-    <t>Weapon_011</t>
-  </si>
-  <si>
-    <t>Weapon_012</t>
-  </si>
-  <si>
-    <t>Weapon_013</t>
-  </si>
-  <si>
-    <t>Weapon_014</t>
-  </si>
-  <si>
-    <t>Weapon_015</t>
-  </si>
-  <si>
     <t>Option_Description</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -403,6 +369,32 @@
   <si>
     <t>Armor</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 갑옷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_003</t>
+  </si>
+  <si>
+    <t>공격 적중 시 화상 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_003</t>
   </si>
 </sst>
 </file>
@@ -514,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -531,6 +523,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -813,10 +806,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
@@ -824,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2">
         <v>10</v>
@@ -848,22 +841,22 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -874,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -898,20 +891,20 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2">
         <v>0</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -922,7 +915,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2">
         <v>10</v>
@@ -946,28 +939,28 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C5" s="9">
         <v>10</v>
@@ -991,43 +984,72 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="9">
+        <v>5</v>
+      </c>
+      <c r="D6" s="9">
+        <v>12</v>
+      </c>
+      <c r="E6" s="9">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="9">
+        <v>5</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
       <c r="N6" s="2"/>
+      <c r="O6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A7" s="2"/>
       <c r="B7" s="7"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1041,9 +1063,7 @@
       <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="A8" s="2"/>
       <c r="B8" s="7"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1057,9 +1077,7 @@
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A9" s="2"/>
       <c r="B9" s="7"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1073,9 +1091,7 @@
       <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="A10" s="2"/>
       <c r="B10" s="7"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1089,9 +1105,7 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="A11" s="2"/>
       <c r="B11" s="7"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1105,9 +1119,7 @@
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="7"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1121,24 +1133,16 @@
       <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="A16" s="2"/>
     </row>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
@@ -2178,7 +2182,7 @@
         <v>13</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -2202,7 +2206,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -2211,30 +2215,30 @@
         <v>100</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2243,30 +2247,30 @@
         <v>100</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2275,22 +2279,22 @@
         <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
@@ -3334,10 +3338,10 @@
         <v>24</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -3360,25 +3364,25 @@
     </row>
     <row r="2" spans="1:26" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -4395,7 +4399,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="26" width="8.7109375" customWidth="1"/>
@@ -4406,47 +4410,56 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580"/>
+    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -347,8 +347,52 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>천으로 만든 갑옷이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철 갑옷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_003</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_003</t>
+  </si>
+  <si>
+    <t>공격 적중 시 화상 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_003</t>
+  </si>
+  <si>
+    <t>Option_004</t>
+  </si>
+  <si>
+    <t>Option_004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_004</t>
+  </si>
+  <si>
     <r>
-      <t>n</t>
+      <t>공격</t>
     </r>
     <r>
       <rPr>
@@ -358,43 +402,125 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ull</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>적중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>적용</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>천으로 만든 갑옷이다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 갑옷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염 검</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_003</t>
-  </si>
-  <si>
-    <t>공격 적중 시 화상 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_003</t>
   </si>
 </sst>
 </file>
@@ -506,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -524,6 +650,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1005,7 +1132,7 @@
         <v>46</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" s="9">
         <v>5</v>
@@ -1029,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K6" s="9">
         <v>5</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M6" s="9">
         <v>0</v>
@@ -2206,7 +2333,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -2276,25 +2403,25 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>5000</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
       <c r="I4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
@@ -4399,7 +4526,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="26" width="8.7109375" customWidth="1"/>
@@ -4449,22 +4576,31 @@
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="2"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429BCC0E-8CCD-4708-9090-0FE7821B9989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11055" yWindow="4125" windowWidth="17310" windowHeight="11580" activeTab="3"/>
+    <workbookView xWindow="1710" yWindow="4815" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="136">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -123,170 +124,114 @@
   </si>
   <si>
     <t>Armor_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>null</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Item_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>빨간 포션</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Item_Description</t>
   </si>
   <si>
     <t>아이템 설명입니다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Item_Price</t>
   </si>
   <si>
     <t>ItemType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Weapon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>One-Handed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>튼튼한 철로 만든 철 갑옷이다 사용자의 몸을 든든하게 지켜준다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Armor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Weapon_004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Weapon_005</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>철로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>만든</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>검</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Option_Description</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>낡은 검</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>나무 활</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>낡은 단검</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>낡은 지팡이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>추가 공격력</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>null</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_002</t>
   </si>
   <si>
     <t>크리티컬 확률 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Armor_002</t>
   </si>
   <si>
     <t>가죽 갑옷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -302,33 +247,33 @@
       </rPr>
       <t>ull</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>단단한 가죽으로 만든 갑옷이다. 사용자의 몸을 지켜준다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_Type</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Passive</t>
   </si>
   <si>
     <t>Option_002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Armor_003</t>
   </si>
   <si>
     <t>천 갑옷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -344,38 +289,38 @@
       </rPr>
       <t>ull</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>천으로 만든 갑옷이다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Armor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>철 갑옷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>화염 검</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_003</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>null</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_003</t>
   </si>
   <si>
     <t>공격 적중 시 화상 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_003</t>
@@ -385,7 +330,7 @@
   </si>
   <si>
     <t>Option_004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_004</t>
@@ -520,18 +465,724 @@
       </rPr>
       <t>적용</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_005</t>
+  </si>
+  <si>
+    <t>Option_006</t>
+  </si>
+  <si>
+    <t>Option_007</t>
+  </si>
+  <si>
+    <t>Option_008</t>
+  </si>
+  <si>
+    <t>Effect_005</t>
+  </si>
+  <si>
+    <t>Effect_006</t>
+  </si>
+  <si>
+    <t>Effect_007</t>
+  </si>
+  <si>
+    <t>Effect_008</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>낡은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 검이다</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Price</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_006</t>
+  </si>
+  <si>
+    <t>Weapon_007</t>
+  </si>
+  <si>
+    <t>Weapon_008</t>
+  </si>
+  <si>
+    <t>Weapon_009</t>
+  </si>
+  <si>
+    <t>Weapon_010</t>
+  </si>
+  <si>
+    <t>Weapon_011</t>
+  </si>
+  <si>
+    <t>Weapon_012</t>
+  </si>
+  <si>
+    <t>Armor_004</t>
+  </si>
+  <si>
+    <t>Armor_005</t>
+  </si>
+  <si>
+    <t>Armor_006</t>
+  </si>
+  <si>
+    <t>Armor_007</t>
+  </si>
+  <si>
+    <t>Armor_008</t>
+  </si>
+  <si>
+    <t>Armor_009</t>
+  </si>
+  <si>
+    <t>Armor_010</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갑옷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷1</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 갑옷7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>테스트 무기1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 무기2</t>
+  </si>
+  <si>
+    <t>테스트 무기3</t>
+  </si>
+  <si>
+    <t>테스트 무기4</t>
+  </si>
+  <si>
+    <t>테스트 무기5</t>
+  </si>
+  <si>
+    <t>테스트 무기6</t>
+  </si>
+  <si>
+    <t>테스트 무기7</t>
+  </si>
+  <si>
+    <t>테스트 무기 1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 무기 2</t>
+  </si>
+  <si>
+    <t>테스트 무기 3</t>
+  </si>
+  <si>
+    <t>테스트 무기 4</t>
+  </si>
+  <si>
+    <t>테스트 무기 5</t>
+  </si>
+  <si>
+    <t>테스트 무기 6</t>
+  </si>
+  <si>
+    <t>테스트 무기 7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -585,6 +1236,20 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -594,7 +1259,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -628,29 +1293,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -865,8 +1543,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -889,7 +1567,7 @@
     <col min="18" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -938,13 +1616,16 @@
       <c r="P1" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="Q1" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2">
         <v>10</v>
@@ -968,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
@@ -980,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>41</v>
@@ -988,13 +1669,16 @@
       <c r="P2" t="b">
         <v>1</v>
       </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" ht="16.5" customHeight="1">
+    <row r="3" spans="1:17" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -1018,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
@@ -1036,13 +1720,16 @@
       <c r="P3" t="b">
         <v>1</v>
       </c>
+      <c r="Q3">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" ht="16.5" customHeight="1">
+    <row r="4" spans="1:17" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2">
         <v>10</v>
@@ -1066,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
@@ -1081,13 +1768,16 @@
       <c r="O4" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="Q4">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" ht="16.5" customHeight="1">
+    <row r="5" spans="1:17" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="9">
         <v>10</v>
@@ -1111,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
@@ -1126,13 +1816,16 @@
       <c r="O5" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" ht="16.5" customHeight="1">
+    <row r="6" spans="1:17" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="9">
         <v>5</v>
@@ -1156,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K6" s="9">
         <v>5</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M6" s="9">
         <v>0</v>
@@ -1174,101 +1867,373 @@
       <c r="P6" t="b">
         <v>1</v>
       </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="9">
+        <v>11</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+    <row r="8" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="9">
+        <v>12</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q8">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="9">
+        <v>13</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q9">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="9">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q10">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+    <row r="11" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="9">
+        <v>15</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q11">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+    <row r="12" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="9">
+        <v>16</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A13" s="2"/>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="9">
+        <v>17</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" spans="1:16" ht="16.5" customHeight="1">
+    <row r="14" spans="1:17" ht="16.5" customHeight="1">
       <c r="A14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q14">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:16" ht="16.5" customHeight="1">
+    <row r="15" spans="1:17" ht="16.5" customHeight="1">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="16.5" customHeight="1">
+    <row r="16" spans="1:17" ht="16.5" customHeight="1">
       <c r="A16" s="2"/>
     </row>
     <row r="17" ht="16.5" customHeight="1"/>
@@ -2256,14 +3221,14 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2277,7 +3242,8 @@
     <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="67.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
@@ -2311,7 +3277,9 @@
       <c r="J1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="3"/>
+      <c r="K1" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -2333,7 +3301,7 @@
         <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -2358,14 +3326,17 @@
       </c>
       <c r="J2" s="7" t="s">
         <v>44</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2374,30 +3345,33 @@
         <v>100</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>44</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2406,33 +3380,272 @@
         <v>5000</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
       <c r="I4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>71</v>
+      <c r="K4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
-      <c r="I5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="6" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11">
+        <v>7</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="13" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="14" spans="1:26" ht="16.5" customHeight="1"/>
@@ -3423,14 +4636,14 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3468,7 +4681,7 @@
         <v>37</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -4514,14 +5727,14 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4537,13 +5750,13 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1">
@@ -4551,65 +5764,95 @@
         <v>32</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="7" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1"/>
     <row r="11" spans="1:4" ht="16.5" customHeight="1"/>
     <row r="12" spans="1:4" ht="16.5" customHeight="1"/>
@@ -5602,7 +6845,7 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429BCC0E-8CCD-4708-9090-0FE7821B9989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE500979-6CAF-4E28-996B-2F7FC21733C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="4815" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Item_Master" sheetId="3" r:id="rId3"/>
     <sheet name="Option_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="2XdxoDNmepd5wUdrOjM5AYD2fl/0TNPY3WAwExGsGHM="/>
@@ -1306,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1322,10 +1322,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1616,7 +1613,7 @@
       <c r="P1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1779,25 +1776,25 @@
       <c r="B5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="2">
         <v>10</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="2">
         <v>1.2</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="2">
         <v>0</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
@@ -1824,44 +1821,44 @@
       <c r="A6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="2">
         <v>12</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="2">
         <v>12</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="2">
         <v>0</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="2">
         <v>5</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="2">
         <v>0</v>
       </c>
       <c r="N6" s="2"/>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P6" t="b">
@@ -1875,40 +1872,40 @@
       <c r="A7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="2">
         <v>11</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="2">
         <v>0.1</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="2">
         <v>0.1</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="2">
         <v>0.1</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="2">
         <v>0.1</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="2">
         <v>0.1</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="2">
         <v>0.1</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="2">
         <v>0</v>
       </c>
       <c r="N7" s="8" t="s">
@@ -1925,40 +1922,40 @@
       <c r="A8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="2">
         <v>12</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="2">
         <v>0.1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="2">
         <v>0.1</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="2">
         <v>0.1</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="2">
         <v>0.1</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="2">
         <v>0.1</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="2">
         <v>0.1</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="2">
         <v>0</v>
       </c>
       <c r="N8" s="8" t="s">
@@ -1975,40 +1972,40 @@
       <c r="A9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="2">
         <v>13</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="2">
         <v>0.1</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="2">
         <v>0.1</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="2">
         <v>0.1</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="2">
         <v>0.1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="2">
         <v>0.1</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="2">
         <v>0.1</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="2">
         <v>0</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="2">
         <v>0</v>
       </c>
       <c r="N9" s="8" t="s">
@@ -2025,40 +2022,40 @@
       <c r="A10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="2">
         <v>14</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="2">
         <v>0.1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="2">
         <v>0.1</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="2">
         <v>0.1</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="2">
         <v>0.1</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="2">
         <v>0.1</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="2">
         <v>0.1</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="2">
         <v>0</v>
       </c>
       <c r="N10" s="8" t="s">
@@ -2075,46 +2072,46 @@
       <c r="A11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="2">
         <v>15</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="2">
         <v>0.1</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="2">
         <v>0.1</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="2">
         <v>0.1</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="2">
         <v>0.1</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="2">
         <v>0.1</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="2">
         <v>0.1</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="2">
         <v>0</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="2">
         <v>0</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="O11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Q11">
@@ -2125,40 +2122,40 @@
       <c r="A12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="2">
         <v>16</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="2">
         <v>0.1</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="2">
         <v>0.1</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="2">
         <v>0.1</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="2">
         <v>0.1</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="2">
         <v>0.1</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="2">
         <v>0.1</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="2">
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
@@ -2175,40 +2172,40 @@
       <c r="A13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="2">
         <v>17</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="2">
         <v>0.1</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="2">
         <v>0.1</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="2">
         <v>0.1</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="2">
         <v>0.1</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="2">
         <v>0.1</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="2">
         <v>0.1</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="2">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="2">
         <v>0</v>
       </c>
       <c r="N13" s="8" t="s">
@@ -3405,7 +3402,7 @@
       <c r="A5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>115</v>
       </c>
       <c r="C5">
@@ -3423,10 +3420,10 @@
       <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="7" t="s">
         <v>108</v>
       </c>
       <c r="J5" s="7" t="s">
@@ -3440,7 +3437,7 @@
       <c r="A6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="10" t="s">
         <v>116</v>
       </c>
       <c r="C6">
@@ -3458,10 +3455,10 @@
       <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="7" t="s">
         <v>109</v>
       </c>
       <c r="J6" s="7" t="s">
@@ -3475,7 +3472,7 @@
       <c r="A7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C7">
@@ -3493,10 +3490,10 @@
       <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="7" t="s">
         <v>110</v>
       </c>
       <c r="J7" s="7" t="s">
@@ -3510,7 +3507,7 @@
       <c r="A8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>118</v>
       </c>
       <c r="C8">
@@ -3528,10 +3525,10 @@
       <c r="G8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="2">
         <v>0</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="7" t="s">
         <v>111</v>
       </c>
       <c r="J8" s="7" t="s">
@@ -3545,7 +3542,7 @@
       <c r="A9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>119</v>
       </c>
       <c r="C9">
@@ -3563,10 +3560,10 @@
       <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="2">
         <v>0</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="7" t="s">
         <v>112</v>
       </c>
       <c r="J9" s="7" t="s">
@@ -3580,7 +3577,7 @@
       <c r="A10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>120</v>
       </c>
       <c r="C10">
@@ -3598,10 +3595,10 @@
       <c r="G10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="7" t="s">
         <v>113</v>
       </c>
       <c r="J10" s="7" t="s">
@@ -3615,7 +3612,7 @@
       <c r="A11" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>121</v>
       </c>
       <c r="C11">
@@ -3633,10 +3630,10 @@
       <c r="G11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="2">
         <v>0</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="7" t="s">
         <v>114</v>
       </c>
       <c r="J11" s="7" t="s">
@@ -5805,7 +5802,7 @@
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -5819,13 +5816,13 @@
       <c r="A6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="2" t="s">
         <v>91</v>
       </c>
     </row>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE500979-6CAF-4E28-996B-2F7FC21733C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AC4047-6195-44B8-8035-8572BFAB3627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1200" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="136">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -2220,12 +2220,7 @@
     </row>
     <row r="14" spans="1:17" ht="16.5" customHeight="1">
       <c r="A14" s="2"/>
-      <c r="O14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q14">
-        <v>5</v>
-      </c>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:17" ht="16.5" customHeight="1">
       <c r="A15" s="2"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AC4047-6195-44B8-8035-8572BFAB3627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4B4A93-F927-438B-BD14-371A5E606F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1200" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="180">
   <si>
     <t>Weapon_ID</t>
   </si>
@@ -1164,6 +1164,208 @@
   </si>
   <si>
     <t>테스트 무기 7</t>
+  </si>
+  <si>
+    <t>Item_002</t>
+  </si>
+  <si>
+    <t>Item_003</t>
+  </si>
+  <si>
+    <t>Item_004</t>
+  </si>
+  <si>
+    <t>Item_005</t>
+  </si>
+  <si>
+    <t>Item_006</t>
+  </si>
+  <si>
+    <t>Item_007</t>
+  </si>
+  <si>
+    <t>Item_008</t>
+  </si>
+  <si>
+    <t>Item_009</t>
+  </si>
+  <si>
+    <t>Item_010</t>
+  </si>
+  <si>
+    <t>Item_011</t>
+  </si>
+  <si>
+    <t>Item_012</t>
+  </si>
+  <si>
+    <t>Item_013</t>
+  </si>
+  <si>
+    <t>Item_014</t>
+  </si>
+  <si>
+    <t>Item_015</t>
+  </si>
+  <si>
+    <t>Item_016</t>
+  </si>
+  <si>
+    <t>Item_017</t>
+  </si>
+  <si>
+    <t>Item_018</t>
+  </si>
+  <si>
+    <t>Item_019</t>
+  </si>
+  <si>
+    <t>Item_020</t>
+  </si>
+  <si>
+    <t>삽</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>곡괭이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무사다리</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰레기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도로롱인형</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트3</t>
+  </si>
+  <si>
+    <t>테스트4</t>
+  </si>
+  <si>
+    <t>테스트5</t>
+  </si>
+  <si>
+    <t>테스트6</t>
+  </si>
+  <si>
+    <t>테스트7</t>
+  </si>
+  <si>
+    <t>테스트8</t>
+  </si>
+  <si>
+    <t>테스트9</t>
+  </si>
+  <si>
+    <t>테스트10</t>
+  </si>
+  <si>
+    <t>테스트11</t>
+  </si>
+  <si>
+    <t>테스트12</t>
+  </si>
+  <si>
+    <t>테스트13</t>
+  </si>
+  <si>
+    <t>테스트14</t>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀엽다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복합니다</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정신력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복합니다</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_007</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1306,7 +1508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1326,6 +1528,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4672,10 +4875,12 @@
       <c r="G1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -4702,10 +4907,10 @@
         <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
@@ -4716,40 +4921,353 @@
       <c r="G2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="5" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="6" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1"/>
-    <row r="18" ht="16.5" customHeight="1"/>
-    <row r="19" ht="16.5" customHeight="1"/>
-    <row r="20" ht="16.5" customHeight="1"/>
-    <row r="21" ht="16.5" customHeight="1"/>
-    <row r="22" ht="16.5" customHeight="1"/>
-    <row r="23" ht="16.5" customHeight="1"/>
-    <row r="24" ht="16.5" customHeight="1"/>
-    <row r="25" ht="16.5" customHeight="1"/>
-    <row r="26" ht="16.5" customHeight="1"/>
-    <row r="27" ht="16.5" customHeight="1"/>
-    <row r="28" ht="16.5" customHeight="1"/>
-    <row r="29" ht="16.5" customHeight="1"/>
-    <row r="30" ht="16.5" customHeight="1"/>
-    <row r="31" ht="16.5" customHeight="1"/>
-    <row r="32" ht="16.5" customHeight="1"/>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="24" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="25" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="26" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="27" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="28" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="30" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="32" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="33" ht="16.5" customHeight="1"/>
     <row r="34" ht="16.5" customHeight="1"/>
     <row r="35" ht="16.5" customHeight="1"/>
@@ -5721,7 +6239,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5825,6 +6343,9 @@
       <c r="A7" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="B7" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="C7" s="2" t="s">
         <v>87</v>
       </c>
@@ -5832,6 +6353,9 @@
     <row r="8" spans="1:4" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>84</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>88</v>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4B4A93-F927-438B-BD14-371A5E606F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Item_Master" sheetId="3" r:id="rId3"/>
     <sheet name="Option_Master" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="2XdxoDNmepd5wUdrOjM5AYD2fl/0TNPY3WAwExGsGHM="/>
@@ -319,10 +318,6 @@
     <t>Option_003</t>
   </si>
   <si>
-    <t>공격 적중 시 화상 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Effect_003</t>
   </si>
   <si>
@@ -334,138 +329,6 @@
   </si>
   <si>
     <t>Effect_004</t>
-  </si>
-  <si>
-    <r>
-      <t>공격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>적중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>버프</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>적용</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Option_005</t>
@@ -1367,11 +1230,19 @@
     <t>Option_007</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>최대 체력 비례 회복</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -1743,7 +1614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1861,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>41</v>
@@ -2073,10 +1944,10 @@
     </row>
     <row r="7" spans="1:17" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2">
         <v>11</v>
@@ -2112,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>41</v>
@@ -2123,10 +1994,10 @@
     </row>
     <row r="8" spans="1:17" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2">
         <v>12</v>
@@ -2162,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>41</v>
@@ -2173,10 +2044,10 @@
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9" s="2">
         <v>13</v>
@@ -2212,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>41</v>
@@ -2223,10 +2094,10 @@
     </row>
     <row r="10" spans="1:17" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C10" s="2">
         <v>14</v>
@@ -2262,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>41</v>
@@ -2273,10 +2144,10 @@
     </row>
     <row r="11" spans="1:17" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2">
         <v>15</v>
@@ -2312,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>41</v>
@@ -2323,10 +2194,10 @@
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C12" s="2">
         <v>16</v>
@@ -2362,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>41</v>
@@ -2373,10 +2244,10 @@
     </row>
     <row r="13" spans="1:17" ht="16.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2">
         <v>17</v>
@@ -2412,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>41</v>
@@ -3423,7 +3294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3575,7 +3446,7 @@
         <v>5000</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3598,10 +3469,10 @@
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3622,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>44</v>
@@ -3633,10 +3504,10 @@
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -3657,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>44</v>
@@ -3668,10 +3539,10 @@
     </row>
     <row r="7" spans="1:26" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -3692,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>44</v>
@@ -3703,10 +3574,10 @@
     </row>
     <row r="8" spans="1:26" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -3727,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>44</v>
@@ -3738,10 +3609,10 @@
     </row>
     <row r="9" spans="1:26" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -3762,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>44</v>
@@ -3773,10 +3644,10 @@
     </row>
     <row r="10" spans="1:26" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -3797,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>44</v>
@@ -3808,10 +3679,10 @@
     </row>
     <row r="11" spans="1:26" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -3832,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>44</v>
@@ -4838,7 +4709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4879,7 +4750,7 @@
         <v>40</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -4907,7 +4778,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4922,7 +4793,7 @@
         <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I2">
         <v>50</v>
@@ -4930,16 +4801,16 @@
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -4947,16 +4818,16 @@
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -4964,16 +4835,16 @@
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -4981,16 +4852,16 @@
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -4998,22 +4869,22 @@
     </row>
     <row r="7" spans="1:26" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -5021,16 +4892,16 @@
     </row>
     <row r="8" spans="1:26" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -5038,16 +4909,16 @@
     </row>
     <row r="9" spans="1:26" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I9">
         <v>10</v>
@@ -5055,16 +4926,16 @@
     </row>
     <row r="10" spans="1:26" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -5072,16 +4943,16 @@
     </row>
     <row r="11" spans="1:26" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -5089,16 +4960,16 @@
     </row>
     <row r="12" spans="1:26" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -5106,16 +4977,16 @@
     </row>
     <row r="13" spans="1:26" ht="16.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -5123,16 +4994,16 @@
     </row>
     <row r="14" spans="1:26" ht="16.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -5140,16 +5011,16 @@
     </row>
     <row r="15" spans="1:26" ht="16.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -5157,16 +5028,16 @@
     </row>
     <row r="16" spans="1:26" ht="16.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -5174,16 +5045,16 @@
     </row>
     <row r="17" spans="1:9" ht="16.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -5191,16 +5062,16 @@
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -5208,16 +5079,16 @@
     </row>
     <row r="19" spans="1:9" ht="16.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -5225,16 +5096,16 @@
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -5242,16 +5113,16 @@
     </row>
     <row r="21" spans="1:9" ht="16.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I21">
         <v>10</v>
@@ -6244,7 +6115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -6302,10 +6173,10 @@
         <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>63</v>
@@ -6313,13 +6184,13 @@
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>63</v>
@@ -6327,46 +6198,46 @@
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D85999-B33A-4B16-A1D5-AEB5AC8DCA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3"/>
+    <workbookView xWindow="-285" yWindow="1815" windowWidth="27870" windowHeight="11085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -304,10 +305,6 @@
   </si>
   <si>
     <t>화염 검</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_003</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1238,11 +1235,15 @@
     <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Option_003</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -1614,7 +1615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1732,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>41</v>
@@ -1920,13 +1921,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="K6" s="2">
         <v>5</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M6" s="2">
         <v>0</v>
@@ -1944,10 +1945,10 @@
     </row>
     <row r="7" spans="1:17" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2">
         <v>11</v>
@@ -1983,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>41</v>
@@ -1994,10 +1995,10 @@
     </row>
     <row r="8" spans="1:17" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2">
         <v>12</v>
@@ -2033,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>41</v>
@@ -2044,10 +2045,10 @@
     </row>
     <row r="9" spans="1:17" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2">
         <v>13</v>
@@ -2083,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>41</v>
@@ -2094,10 +2095,10 @@
     </row>
     <row r="10" spans="1:17" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2">
         <v>14</v>
@@ -2133,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>41</v>
@@ -2144,10 +2145,10 @@
     </row>
     <row r="11" spans="1:17" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="2">
         <v>15</v>
@@ -2183,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>41</v>
@@ -2194,10 +2195,10 @@
     </row>
     <row r="12" spans="1:17" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2">
         <v>16</v>
@@ -2233,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>41</v>
@@ -2244,10 +2245,10 @@
     </row>
     <row r="13" spans="1:17" ht="16.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2">
         <v>17</v>
@@ -2283,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>41</v>
@@ -3294,7 +3295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -3446,7 +3447,7 @@
         <v>5000</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3469,10 +3470,10 @@
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3493,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>44</v>
@@ -3504,10 +3505,10 @@
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -3528,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>44</v>
@@ -3539,10 +3540,10 @@
     </row>
     <row r="7" spans="1:26" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -3563,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>44</v>
@@ -3574,10 +3575,10 @@
     </row>
     <row r="8" spans="1:26" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -3598,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>44</v>
@@ -3609,10 +3610,10 @@
     </row>
     <row r="9" spans="1:26" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -3633,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>44</v>
@@ -3644,10 +3645,10 @@
     </row>
     <row r="10" spans="1:26" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -3668,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>44</v>
@@ -3679,10 +3680,10 @@
     </row>
     <row r="11" spans="1:26" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -3703,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>44</v>
@@ -4709,7 +4710,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -4750,7 +4751,7 @@
         <v>40</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -4778,7 +4779,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4793,7 +4794,7 @@
         <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I2">
         <v>50</v>
@@ -4801,16 +4802,16 @@
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -4818,16 +4819,16 @@
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -4835,16 +4836,16 @@
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -4852,16 +4853,16 @@
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -4869,22 +4870,22 @@
     </row>
     <row r="7" spans="1:26" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" t="s">
         <v>173</v>
-      </c>
-      <c r="H7" t="s">
-        <v>174</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -4892,16 +4893,16 @@
     </row>
     <row r="8" spans="1:26" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -4909,16 +4910,16 @@
     </row>
     <row r="9" spans="1:26" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I9">
         <v>10</v>
@@ -4926,16 +4927,16 @@
     </row>
     <row r="10" spans="1:26" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -4943,16 +4944,16 @@
     </row>
     <row r="11" spans="1:26" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -4960,16 +4961,16 @@
     </row>
     <row r="12" spans="1:26" ht="16.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -4977,16 +4978,16 @@
     </row>
     <row r="13" spans="1:26" ht="16.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -4994,16 +4995,16 @@
     </row>
     <row r="14" spans="1:26" ht="16.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -5011,16 +5012,16 @@
     </row>
     <row r="15" spans="1:26" ht="16.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -5028,16 +5029,16 @@
     </row>
     <row r="16" spans="1:26" ht="16.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -5045,16 +5046,16 @@
     </row>
     <row r="17" spans="1:9" ht="16.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -5062,16 +5063,16 @@
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -5079,16 +5080,16 @@
     </row>
     <row r="19" spans="1:9" ht="16.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -5096,16 +5097,16 @@
     </row>
     <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -5113,16 +5114,16 @@
     </row>
     <row r="21" spans="1:9" ht="16.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I21">
         <v>10</v>
@@ -6115,7 +6116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -6170,13 +6171,13 @@
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>63</v>
@@ -6184,13 +6185,13 @@
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>63</v>
@@ -6198,46 +6199,46 @@
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D85999-B33A-4B16-A1D5-AEB5AC8DCA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009296BD-E754-4D8E-9120-F4B4D346EE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-285" yWindow="1815" windowWidth="27870" windowHeight="11085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="4290" windowWidth="38160" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="2XdxoDNmepd5wUdrOjM5AYD2fl/0TNPY3WAwExGsGHM="/>
     </ext>
@@ -1940,7 +1943,7 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,1336 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009296BD-E754-4D8E-9120-F4B4D346EE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="4290" windowWidth="38160" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="4290" windowWidth="38160" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Armor_Master" sheetId="2" r:id="rId2"/>
-    <sheet name="Item_Master" sheetId="3" r:id="rId3"/>
-    <sheet name="Option_Master" sheetId="4" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon_Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor_Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item_Master" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option_Master" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="2XdxoDNmepd5wUdrOjM5AYD2fl/0TNPY3WAwExGsGHM="/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="180">
-  <si>
-    <t>Weapon_ID</t>
-  </si>
-  <si>
-    <t>Weapon_Name</t>
-  </si>
-  <si>
-    <t>Weapon_DMG</t>
-  </si>
-  <si>
-    <t>STR_Scaling</t>
-  </si>
-  <si>
-    <t>DEX_Scaling</t>
-  </si>
-  <si>
-    <t>INT_Scaling</t>
-  </si>
-  <si>
-    <t>MAG_Scaling</t>
-  </si>
-  <si>
-    <t>DIV_Scaling</t>
-  </si>
-  <si>
-    <t>CHR_Scaling</t>
-  </si>
-  <si>
-    <t>Option_1_ID</t>
-  </si>
-  <si>
-    <t>Option_Value1</t>
-  </si>
-  <si>
-    <t>Option_2_ID</t>
-  </si>
-  <si>
-    <t>Option_Value2</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Weapon_001</t>
-  </si>
-  <si>
-    <t>Weapon_002</t>
-  </si>
-  <si>
-    <t>Weapon_003</t>
-  </si>
-  <si>
-    <t>Armor_ID</t>
-  </si>
-  <si>
-    <t>Armor_NAME</t>
-  </si>
-  <si>
-    <t>Armor_DEF</t>
-  </si>
-  <si>
-    <t>Armor_HP</t>
-  </si>
-  <si>
-    <t>Armor_Option1</t>
-  </si>
-  <si>
-    <t>Option1_Value</t>
-  </si>
-  <si>
-    <t>Armor_Option2</t>
-  </si>
-  <si>
-    <t>Option2_Value</t>
-  </si>
-  <si>
-    <t>Item_ID</t>
-  </si>
-  <si>
-    <t>Item_NAME</t>
-  </si>
-  <si>
-    <t>Item_Option1</t>
-  </si>
-  <si>
-    <t>Item_Option2</t>
-  </si>
-  <si>
-    <t>Option_ID</t>
-  </si>
-  <si>
-    <t>Effect_ID</t>
-  </si>
-  <si>
-    <t>Armor_001</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_001</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_001</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>빨간 포션</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_005</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Description</t>
-  </si>
-  <si>
-    <t>아이템 설명입니다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Price</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>One-Handed</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>튼튼한 철로 만든 철 갑옷이다 사용자의 몸을 든든하게 지켜준다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_004</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_005</t>
-  </si>
-  <si>
-    <t>Option_Description</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>낡은 검</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 활</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>낡은 단검</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>낡은 지팡이</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 공격력</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_001</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_002</t>
-  </si>
-  <si>
-    <t>크리티컬 확률 증가</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor_002</t>
-  </si>
-  <si>
-    <t>가죽 갑옷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_002</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ull</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>단단한 가죽으로 만든 갑옷이다. 사용자의 몸을 지켜준다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_Type</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-  </si>
-  <si>
-    <t>Option_002</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor_003</t>
-  </si>
-  <si>
-    <t>천 갑옷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ull</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>천으로 만든 갑옷이다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 갑옷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염 검</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_003</t>
-  </si>
-  <si>
-    <t>Effect_003</t>
-  </si>
-  <si>
-    <t>Option_004</t>
-  </si>
-  <si>
-    <t>Option_004</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_004</t>
-  </si>
-  <si>
-    <t>Option_005</t>
-  </si>
-  <si>
-    <t>Option_006</t>
-  </si>
-  <si>
-    <t>Option_007</t>
-  </si>
-  <si>
-    <t>Option_008</t>
-  </si>
-  <si>
-    <t>Effect_005</t>
-  </si>
-  <si>
-    <t>Effect_006</t>
-  </si>
-  <si>
-    <t>Effect_007</t>
-  </si>
-  <si>
-    <t>Effect_008</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">공격 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>속도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>낡은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 검이다</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Price</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon_006</t>
-  </si>
-  <si>
-    <t>Weapon_007</t>
-  </si>
-  <si>
-    <t>Weapon_008</t>
-  </si>
-  <si>
-    <t>Weapon_009</t>
-  </si>
-  <si>
-    <t>Weapon_010</t>
-  </si>
-  <si>
-    <t>Weapon_011</t>
-  </si>
-  <si>
-    <t>Weapon_012</t>
-  </si>
-  <si>
-    <t>Armor_004</t>
-  </si>
-  <si>
-    <t>Armor_005</t>
-  </si>
-  <si>
-    <t>Armor_006</t>
-  </si>
-  <si>
-    <t>Armor_007</t>
-  </si>
-  <si>
-    <t>Armor_008</t>
-  </si>
-  <si>
-    <t>Armor_009</t>
-  </si>
-  <si>
-    <t>Armor_010</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">테스트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>갑옷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷1</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 갑옷7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <t>테스트 무기1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트 무기2</t>
-  </si>
-  <si>
-    <t>테스트 무기3</t>
-  </si>
-  <si>
-    <t>테스트 무기4</t>
-  </si>
-  <si>
-    <t>테스트 무기5</t>
-  </si>
-  <si>
-    <t>테스트 무기6</t>
-  </si>
-  <si>
-    <t>테스트 무기7</t>
-  </si>
-  <si>
-    <t>테스트 무기 1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트 무기 2</t>
-  </si>
-  <si>
-    <t>테스트 무기 3</t>
-  </si>
-  <si>
-    <t>테스트 무기 4</t>
-  </si>
-  <si>
-    <t>테스트 무기 5</t>
-  </si>
-  <si>
-    <t>테스트 무기 6</t>
-  </si>
-  <si>
-    <t>테스트 무기 7</t>
-  </si>
-  <si>
-    <t>Item_002</t>
-  </si>
-  <si>
-    <t>Item_003</t>
-  </si>
-  <si>
-    <t>Item_004</t>
-  </si>
-  <si>
-    <t>Item_005</t>
-  </si>
-  <si>
-    <t>Item_006</t>
-  </si>
-  <si>
-    <t>Item_007</t>
-  </si>
-  <si>
-    <t>Item_008</t>
-  </si>
-  <si>
-    <t>Item_009</t>
-  </si>
-  <si>
-    <t>Item_010</t>
-  </si>
-  <si>
-    <t>Item_011</t>
-  </si>
-  <si>
-    <t>Item_012</t>
-  </si>
-  <si>
-    <t>Item_013</t>
-  </si>
-  <si>
-    <t>Item_014</t>
-  </si>
-  <si>
-    <t>Item_015</t>
-  </si>
-  <si>
-    <t>Item_016</t>
-  </si>
-  <si>
-    <t>Item_017</t>
-  </si>
-  <si>
-    <t>Item_018</t>
-  </si>
-  <si>
-    <t>Item_019</t>
-  </si>
-  <si>
-    <t>Item_020</t>
-  </si>
-  <si>
-    <t>삽</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>곡괭이</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무사다리</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>쓰레기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도로롱인형</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트3</t>
-  </si>
-  <si>
-    <t>테스트4</t>
-  </si>
-  <si>
-    <t>테스트5</t>
-  </si>
-  <si>
-    <t>테스트6</t>
-  </si>
-  <si>
-    <t>테스트7</t>
-  </si>
-  <si>
-    <t>테스트8</t>
-  </si>
-  <si>
-    <t>테스트9</t>
-  </si>
-  <si>
-    <t>테스트10</t>
-  </si>
-  <si>
-    <t>테스트11</t>
-  </si>
-  <si>
-    <t>테스트12</t>
-  </si>
-  <si>
-    <t>테스트13</t>
-  </si>
-  <si>
-    <t>테스트14</t>
-  </si>
-  <si>
-    <t>Item</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>귀엽다!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumable</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체력을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회복합니다</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정신력을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회복합니다</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_007</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력 비례 회복</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Option_003</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="11">
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Malgun Gothic"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
+      <name val="Noto Sans KR"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="굴림"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="굴림"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -1384,40 +156,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1618,693 +449,924 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="113" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="26" width="8.7109375" customWidth="1"/>
+    <col width="12.5703125" customWidth="1" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="14.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="14" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="14" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="14.85546875" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="14.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="14.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="113" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="16.42578125" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="14.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="8.7109375" customWidth="1" min="18" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="16.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Weapon_DMG</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>STR_Scaling</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DEX_Scaling</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>INT_Scaling</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MAG_Scaling</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DIV_Scaling</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CHR_Scaling</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Option_1_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Option_Value1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Option_2_ID</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Option_Value2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>One-Handed</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>Item_Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>낡은 검</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>41</v>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>낡은 검이다</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_002</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>나무 활</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="2">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Option_005</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="2">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
-        <v>41</v>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="2">
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>낡은 단검</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="2">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="2">
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>낡은 지팡이</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="2">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5">
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="2">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>화염 검</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Option_003</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M6" s="2">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
-        <v>41</v>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="2">
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7">
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 1</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="2">
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="2">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8">
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 2</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="2">
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="2">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="2">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N9" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9">
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 3</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="2">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="2">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q10">
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 4</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="2">
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기5</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="2">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11">
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 5</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="2">
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기6</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="2">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q12">
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 6</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="2">
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>테스트 무기7</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="2">
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" s="2">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q13">
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>테스트 무기 7</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="O14" s="2"/>
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Option_003</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Option_003</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>Test weapon: applies burn on hit</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A15" s="2"/>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="2" t="n"/>
     </row>
-    <row r="16" spans="1:17" ht="16.5" customHeight="1">
-      <c r="A16" s="2"/>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="2" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
@@ -3291,436 +2353,581 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="26" width="8.7109375" customWidth="1"/>
+    <col width="11.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="18.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="67.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="12.7109375" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="8.7109375" customWidth="1" min="12" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
+    <row r="1" ht="16.5" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Armor_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Armor_NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Armor_DEF</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Armor_HP</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Armor_Option1</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Option1_Value</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Armor_Option2</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Option2_Value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Item_Price</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
+      <c r="P1" s="3" t="n"/>
+      <c r="Q1" s="3" t="n"/>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
+      <c r="X1" s="3" t="n"/>
+      <c r="Y1" s="3" t="n"/>
+      <c r="Z1" s="3" t="n"/>
     </row>
-    <row r="2" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2">
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Armor_001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>철 갑옷</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Option_001</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="2">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2">
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>튼튼한 철로 만든 철 갑옷이다 사용자의 몸을 든든하게 지켜준다</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3">
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Armor_002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>가죽 갑옷</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Option_002</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>90</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="2">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3">
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>단단한 가죽으로 만든 갑옷이다. 사용자의 몸을 지켜준다</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4">
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Armor_003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>천 갑옷</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>5000</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Option_004</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="2">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4">
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>천으로 만든 갑옷이다</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5">
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Armor_004</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5">
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 1</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Armor_005</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6">
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 2</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7">
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Armor_006</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7">
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 3</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8">
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Armor_007</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8">
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 4</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9">
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Armor_008</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>5</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9">
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 5</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Armor_009</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷6</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="2">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10">
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 6</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11">
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Armor_010</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>테스트 갑옷7</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>7</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11">
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>테스트 갑옷 7</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="12" ht="16.5" customHeight="1"/>
+    <row r="13" ht="16.5" customHeight="1"/>
+    <row r="14" ht="16.5" customHeight="1"/>
+    <row r="15" ht="16.5" customHeight="1"/>
+    <row r="16" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -4706,443 +3913,630 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="26" width="8.7109375" customWidth="1"/>
+    <col width="9.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="14.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="16.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="16.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="20.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="12.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="8.7109375" customWidth="1" min="9" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
+    <row r="1" ht="16.5" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Item_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Item_NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Item_Option1</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Option1_Value</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Item_Option2</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Option2_Value</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Item_Description</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Item_Price</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
+      <c r="P1" s="3" t="n"/>
+      <c r="Q1" s="3" t="n"/>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
+      <c r="X1" s="3" t="n"/>
+      <c r="Y1" s="3" t="n"/>
+      <c r="Z1" s="3" t="n"/>
     </row>
-    <row r="2" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2">
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Item_001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>빨간 포션</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Option_006</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I3">
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Item_002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>삽</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I4">
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Item_003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>곡괭이</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I5">
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Item_004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>나무사다리</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I6">
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Item_005</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>쓰레기</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7">
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Item_006</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>도로롱인형</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Option_007</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>귀엽다!</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I8">
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Item_007</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>테스트1</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9">
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Item_008</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>테스트2</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10">
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Item_009</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>테스트3</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I11">
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Item_010</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>테스트4</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I12">
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Item_011</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>테스트5</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I13">
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Item_012</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>테스트6</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I14">
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Item_013</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>테스트7</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I15">
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Item_014</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>테스트8</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I16">
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Item_015</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>테스트9</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I17">
+    <row r="17" ht="16.5" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Item_016</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>테스트10</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I18">
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Item_017</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>테스트11</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I19">
+    <row r="19" ht="16.5" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Item_018</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>테스트12</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I20">
+    <row r="20" ht="16.5" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Item_019</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>테스트13</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I21">
+    <row r="21" ht="16.5" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Item_020</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>테스트14</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>아이템 설명입니다</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="24" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="25" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="26" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="27" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="28" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="30" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:9" ht="16.5" customHeight="1"/>
-    <row r="32" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="22" ht="16.5" customHeight="1"/>
+    <row r="23" ht="16.5" customHeight="1"/>
+    <row r="24" ht="16.5" customHeight="1"/>
+    <row r="25" ht="16.5" customHeight="1"/>
+    <row r="26" ht="16.5" customHeight="1"/>
+    <row r="27" ht="16.5" customHeight="1"/>
+    <row r="28" ht="16.5" customHeight="1"/>
+    <row r="29" ht="16.5" customHeight="1"/>
+    <row r="30" ht="16.5" customHeight="1"/>
+    <row r="31" ht="16.5" customHeight="1"/>
+    <row r="32" ht="16.5" customHeight="1"/>
     <row r="33" ht="16.5" customHeight="1"/>
     <row r="34" ht="16.5" customHeight="1"/>
     <row r="35" ht="16.5" customHeight="1"/>
@@ -6112,145 +5506,212 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="26" width="8.7109375" customWidth="1"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="34.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="14.28515625" customWidth="1" min="4" max="4"/>
+    <col width="8.7109375" customWidth="1" min="5" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
+    <row r="1" ht="16.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Option_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Option_Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Effect_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Option_Type</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>63</v>
+    <row r="2" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Option_001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>추가 공격력</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Effect_001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>64</v>
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Option_002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>크리티컬 확률 증가</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Effect_002</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>63</v>
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Option_003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Effect_003</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>63</v>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Option_004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>최대 체력 비례 회복</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Effect_004</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>88</v>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Option_005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>공격 속도 증가</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Effect_005</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>84</v>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Option_006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>체력을 회복합니다</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Effect_006</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>85</v>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Option_007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>정신력을 회복합니다</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Effect_007</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>86</v>
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Option_008</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Effect_008</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:4" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="10" ht="16.5" customHeight="1"/>
+    <row r="11" ht="16.5" customHeight="1"/>
+    <row r="12" ht="16.5" customHeight="1"/>
+    <row r="13" ht="16.5" customHeight="1"/>
+    <row r="14" ht="16.5" customHeight="1"/>
+    <row r="15" ht="16.5" customHeight="1"/>
+    <row r="16" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -7236,8 +6697,7 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Option_003</t>
+          <t>화염 검</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Test weapon: applies burn on hit</t>
+          <t>공격 적중 시 화상을 부여하는 테스트 무기</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5548,6 +5548,81 @@
           <t>Option_Type</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>StatusType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ApplyMode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>StackPolicy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MaxStack</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TickInterval</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TriggerType</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ValueMode</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>BaseChance</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ChancePerStack</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>BaseValue</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ValuePerStack</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ResistanceType</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>MaxRemoveCount</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -5570,6 +5645,55 @@
           <t>OnHit</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AddDamage</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -5592,6 +5716,60 @@
           <t>Passive</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CriticalChance</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CritChance</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -5614,6 +5792,55 @@
           <t>OnHit</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TimedTick</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>OnTick</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -5636,6 +5863,55 @@
           <t>OnHit</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HealOverTime</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TimedTick</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>OnTick</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -5658,6 +5934,60 @@
           <t>Passive</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -5675,6 +6005,55 @@
           <t>Effect_006</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OneShotHPHeal</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>OnUse</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -5692,6 +6071,55 @@
           <t>Effect_007</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OneShotMPHeal</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OnUse</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -5699,17 +6127,446 @@
           <t>Option_008</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>적중 시 대상의 다음 공격 1회 실패</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Effect_008</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ForcedMiss</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OneShotState</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BeforeAttack</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>StackCount</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1"/>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Option_009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>출혈: 공격 시 스택 기반 확률로 최대 체력 비례 고정 피해</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Effect_009</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bleed</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>99</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>BleedResist</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Option_010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>중독: 공격 시 스택 기반 확률로 최대 체력 비례 피해</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Effect_010</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>99</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>PoisonResist</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Option_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>신성: 공격 시 적 명중률 감소 및 자기 디버프 정화</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Effect_011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Holy</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>99</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Option_012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>재생: 공격 시 스택 기반 확률로 최대 체력 비례 회복</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Effect_012</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Regen</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>99</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Option_013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>빙결: 행동 전 확률로 행동 불가 및 속도 감소</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Effect_013</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>BeforeAttack</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>FreezeResist</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="15" ht="16.5" customHeight="1"/>
     <row r="16" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor_Master" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item_Master" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option_Master" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OptionEffect_Master" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -2364,21 +2365,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="11.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="12.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="18.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="18.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="67.140625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="12.7109375" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="8.7109375" customWidth="1" min="12" max="26"/>
+    <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="15" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="15" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="13" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="12" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="26"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1">
@@ -2923,7 +2938,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1"/>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Armor_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>저항 테스트 갑옷</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Option_014</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Option_015</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>디버프 피해/출혈 저항 연결 테스트용 갑옷</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="13" ht="16.5" customHeight="1"/>
     <row r="14" ht="16.5" customHeight="1"/>
     <row r="15" ht="16.5" customHeight="1"/>
@@ -5517,679 +5578,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="34.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="19.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="14.28515625" customWidth="1" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="8.7109375" customWidth="1" min="5" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Option_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Option_Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Effect_ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Option_Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>StatusType</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ApplyMode</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>StackPolicy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>MaxStack</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>TickInterval</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>TriggerType</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ValueMode</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>BaseChance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ChancePerStack</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>BaseValue</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ValuePerStack</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ResistanceType</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>MaxRemoveCount</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Option_001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>추가 공격력</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Effect_001</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>OnHit</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AddDamage</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+    </row>
+    <row r="3" ht="16.5" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Option_002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>크리티컬 확률 증가</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Effect_002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16.5" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Option_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Effect_003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>OnHit</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Option_002</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>크리티컬 확률 증가</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Effect_002</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Option_004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>최대 체력 비례 회복</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Effect_004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Option_005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>공격 속도 증가</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Effect_005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CriticalChance</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CritChance</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Option_003</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Effect_003</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Option_006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>체력을 회복합니다</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Effect_006</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Option_007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>정신력을 회복합니다</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Effect_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Option_008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>적중 시 대상의 다음 공격 1회 실패</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Effect_008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>OnHit</t>
         </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Burn</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TimedTick</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Refresh</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>OnTick</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Option_004</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>최대 체력 비례 회복</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Effect_004</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HealOverTime</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TimedTick</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Refresh</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>OnTick</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Option_005</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>공격 속도 증가</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Effect_005</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AttackSpeed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Option_006</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>체력을 회복합니다</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Effect_006</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OneShotHPHeal</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>OnUse</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Option_007</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>정신력을 회복합니다</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Effect_007</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>OneShotMPHeal</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>OnUse</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Option_008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>적중 시 대상의 다음 공격 1회 실패</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Effect_008</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ForcedMiss</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OneShotState</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>99</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>BeforeAttack</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>StackCount</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1">
@@ -6213,60 +5797,6 @@
           <t>OnHit</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Bleed</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>99</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>BleedResist</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -6289,60 +5819,6 @@
           <t>OnHit</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Poison</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>99</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>100</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>PoisonResist</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -6365,55 +5841,6 @@
           <t>OnHit</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Holy</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>99</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -6436,55 +5863,6 @@
           <t>OnHit</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Regen</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>99</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>100</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -6507,70 +5885,95 @@
           <t>OnHit</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>BeforeAttack</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>10</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>FreezeResist</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1"/>
-    <row r="18" ht="16.5" customHeight="1"/>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Option_014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>디버프 피해 저항</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Effect_014</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Option_015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>출혈 저항</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Effect_014</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Option_016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>중독 저항</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Effect_014</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Option_017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>빙결 저항</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Effect_014</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="16.5" customHeight="1"/>
     <row r="20" ht="16.5" customHeight="1"/>
     <row r="21" ht="16.5" customHeight="1"/>
@@ -7557,4 +6960,1120 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Option_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>StatusType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ApplyMode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>StackPolicy</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MaxStack</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TickInterval</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TriggerType</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ValueMode</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>BaseChance</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ChancePerStack</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>BaseValue</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ValuePerStack</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>StatType</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ResistanceType</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>MaxRemoveCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Option_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AddDamage</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Option_002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CriticalChance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>CritChance</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Option_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TimedTick</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OnTick</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Option_004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HealOverTime</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TimedTick</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Refresh</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OnTick</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Option_005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AttackSpeed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Option_006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OneShotHPHeal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OnUse</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Option_007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OneShotMPHeal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OnUse</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Option_008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ForcedMiss</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OneShotState</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>99</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BeforeAttack</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>StackCount</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Option_009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bleed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>BleedResist</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Option_010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PoisonResist</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Option_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Holy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>99</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Option_012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Regen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>99</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PercentMaxHP</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Option_013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Stacking</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BeforeAttack</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FreezeResist</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Option_014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DebuffDamageResist</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>DebuffDamageResist</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Option_015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BleedResist</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BleedResist</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Option_016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PoisonResist</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>PoisonResist</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Option_017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FreezeResist</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OnEquip</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>FreezeResist</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
+++ b/JsonFile/Assets/ExcelFiles/AllItem_Master.xlsx
@@ -1,109 +1,887 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\Unity\Adventure\JsonFile\Assets\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95C4316-32E3-4494-A492-E34D0262707A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="4290" windowWidth="38160" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon_Master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armor_Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item_Master" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option_Master" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OptionEffect_Master" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Weapon_Master" sheetId="1" r:id="rId1"/>
+    <sheet name="Armor_Master" sheetId="2" r:id="rId2"/>
+    <sheet name="Item_Master" sheetId="3" r:id="rId3"/>
+    <sheet name="Option_Master" sheetId="4" r:id="rId4"/>
+    <sheet name="OptionEffect_Master" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="258">
+  <si>
+    <t>Option_ID</t>
+  </si>
+  <si>
+    <t>StatusType</t>
+  </si>
+  <si>
+    <t>ApplyMode</t>
+  </si>
+  <si>
+    <t>StackPolicy</t>
+  </si>
+  <si>
+    <t>MaxStack</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>TickInterval</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+  </si>
+  <si>
+    <t>ValueMode</t>
+  </si>
+  <si>
+    <t>BaseChance</t>
+  </si>
+  <si>
+    <t>ChancePerStack</t>
+  </si>
+  <si>
+    <t>BaseValue</t>
+  </si>
+  <si>
+    <t>ValuePerStack</t>
+  </si>
+  <si>
+    <t>StatType</t>
+  </si>
+  <si>
+    <t>ResistanceType</t>
+  </si>
+  <si>
+    <t>MaxRemoveCount</t>
+  </si>
+  <si>
+    <t>Option_001</t>
+  </si>
+  <si>
+    <t>AddDamage</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>OnHit</t>
+  </si>
+  <si>
+    <t>Flat</t>
+  </si>
+  <si>
+    <t>Option_002</t>
+  </si>
+  <si>
+    <t>CriticalChance</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Ignore</t>
+  </si>
+  <si>
+    <t>OnEquip</t>
+  </si>
+  <si>
+    <t>CritChance</t>
+  </si>
+  <si>
+    <t>Option_003</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>TimedTick</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>OnTick</t>
+  </si>
+  <si>
+    <t>PercentMaxHP</t>
+  </si>
+  <si>
+    <t>Option_004</t>
+  </si>
+  <si>
+    <t>HealOverTime</t>
+  </si>
+  <si>
+    <t>Option_005</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Option_006</t>
+  </si>
+  <si>
+    <t>OneShotHPHeal</t>
+  </si>
+  <si>
+    <t>OnUse</t>
+  </si>
+  <si>
+    <t>Option_007</t>
+  </si>
+  <si>
+    <t>OneShotMPHeal</t>
+  </si>
+  <si>
+    <t>Option_008</t>
+  </si>
+  <si>
+    <t>ForcedMiss</t>
+  </si>
+  <si>
+    <t>OneShotState</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>BeforeAttack</t>
+  </si>
+  <si>
+    <t>StackCount</t>
+  </si>
+  <si>
+    <t>Option_009</t>
+  </si>
+  <si>
+    <t>Bleed</t>
+  </si>
+  <si>
+    <t>Stacking</t>
+  </si>
+  <si>
+    <t>OnAttack</t>
+  </si>
+  <si>
+    <t>BleedResist</t>
+  </si>
+  <si>
+    <t>Option_010</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>PoisonResist</t>
+  </si>
+  <si>
+    <t>Option_011</t>
+  </si>
+  <si>
+    <t>Holy</t>
+  </si>
+  <si>
+    <t>Option_012</t>
+  </si>
+  <si>
+    <t>Regen</t>
+  </si>
+  <si>
+    <t>Option_013</t>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>FreezeResist</t>
+  </si>
+  <si>
+    <t>Option_014</t>
+  </si>
+  <si>
+    <t>DebuffDamageResist</t>
+  </si>
+  <si>
+    <t>Stat</t>
+  </si>
+  <si>
+    <t>Option_015</t>
+  </si>
+  <si>
+    <t>Option_016</t>
+  </si>
+  <si>
+    <t>Option_017</t>
+  </si>
+  <si>
+    <t>Option_018</t>
+  </si>
+  <si>
+    <t>Berserk</t>
+  </si>
+  <si>
+    <t>Compound</t>
+  </si>
+  <si>
+    <t>OnBattleStart</t>
+  </si>
+  <si>
+    <t>Weapon_ID</t>
+  </si>
+  <si>
+    <t>Weapon_Name</t>
+  </si>
+  <si>
+    <t>Weapon_DMG</t>
+  </si>
+  <si>
+    <t>STR_Scaling</t>
+  </si>
+  <si>
+    <t>DEX_Scaling</t>
+  </si>
+  <si>
+    <t>INT_Scaling</t>
+  </si>
+  <si>
+    <t>MAG_Scaling</t>
+  </si>
+  <si>
+    <t>DIV_Scaling</t>
+  </si>
+  <si>
+    <t>CHR_Scaling</t>
+  </si>
+  <si>
+    <t>Option_1_ID</t>
+  </si>
+  <si>
+    <t>Option_Value1</t>
+  </si>
+  <si>
+    <t>Option_2_ID</t>
+  </si>
+  <si>
+    <t>Option_Value2</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>One-Handed</t>
+  </si>
+  <si>
+    <t>Item_Price</t>
+  </si>
+  <si>
+    <t>Weapon_001</t>
+  </si>
+  <si>
+    <t>낡은 검</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>낡은 검이다</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>Weapon_002</t>
+  </si>
+  <si>
+    <t>나무 활</t>
+  </si>
+  <si>
+    <t>Weapon_003</t>
+  </si>
+  <si>
+    <t>낡은 단검</t>
+  </si>
+  <si>
+    <t>Weapon_004</t>
+  </si>
+  <si>
+    <t>낡은 지팡이</t>
+  </si>
+  <si>
+    <t>Weapon_005</t>
+  </si>
+  <si>
+    <t>화염 검</t>
+  </si>
+  <si>
+    <t>Weapon_006</t>
+  </si>
+  <si>
+    <t>테스트 무기1</t>
+  </si>
+  <si>
+    <t>테스트 무기 1</t>
+  </si>
+  <si>
+    <t>Weapon_007</t>
+  </si>
+  <si>
+    <t>테스트 무기2</t>
+  </si>
+  <si>
+    <t>테스트 무기 2</t>
+  </si>
+  <si>
+    <t>Weapon_008</t>
+  </si>
+  <si>
+    <t>테스트 무기3</t>
+  </si>
+  <si>
+    <t>테스트 무기 3</t>
+  </si>
+  <si>
+    <t>Weapon_009</t>
+  </si>
+  <si>
+    <t>테스트 무기4</t>
+  </si>
+  <si>
+    <t>테스트 무기 4</t>
+  </si>
+  <si>
+    <t>Weapon_010</t>
+  </si>
+  <si>
+    <t>테스트 무기5</t>
+  </si>
+  <si>
+    <t>테스트 무기 5</t>
+  </si>
+  <si>
+    <t>Weapon_011</t>
+  </si>
+  <si>
+    <t>테스트 무기6</t>
+  </si>
+  <si>
+    <t>테스트 무기 6</t>
+  </si>
+  <si>
+    <t>Weapon_012</t>
+  </si>
+  <si>
+    <t>테스트 무기7</t>
+  </si>
+  <si>
+    <t>테스트 무기 7</t>
+  </si>
+  <si>
+    <t>Weapon_013</t>
+  </si>
+  <si>
+    <t>공격 적중 시 화상을 부여하는 테스트 무기</t>
+  </si>
+  <si>
+    <t>Armor_ID</t>
+  </si>
+  <si>
+    <t>Armor_NAME</t>
+  </si>
+  <si>
+    <t>Armor_DEF</t>
+  </si>
+  <si>
+    <t>Armor_HP</t>
+  </si>
+  <si>
+    <t>Armor_Option1</t>
+  </si>
+  <si>
+    <t>Option1_Value</t>
+  </si>
+  <si>
+    <t>Armor_Option2</t>
+  </si>
+  <si>
+    <t>Option2_Value</t>
+  </si>
+  <si>
+    <t>Armor_001</t>
+  </si>
+  <si>
+    <t>철 갑옷</t>
+  </si>
+  <si>
+    <t>튼튼한 철로 만든 철 갑옷이다 사용자의 몸을 든든하게 지켜준다</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Armor_002</t>
+  </si>
+  <si>
+    <t>가죽 갑옷</t>
+  </si>
+  <si>
+    <t>단단한 가죽으로 만든 갑옷이다. 사용자의 몸을 지켜준다</t>
+  </si>
+  <si>
+    <t>Armor_003</t>
+  </si>
+  <si>
+    <t>천 갑옷</t>
+  </si>
+  <si>
+    <t>천으로 만든 갑옷이다</t>
+  </si>
+  <si>
+    <t>Armor_004</t>
+  </si>
+  <si>
+    <t>테스트 갑옷1</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 1</t>
+  </si>
+  <si>
+    <t>Armor_005</t>
+  </si>
+  <si>
+    <t>테스트 갑옷2</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 2</t>
+  </si>
+  <si>
+    <t>Armor_006</t>
+  </si>
+  <si>
+    <t>테스트 갑옷3</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 3</t>
+  </si>
+  <si>
+    <t>Armor_007</t>
+  </si>
+  <si>
+    <t>테스트 갑옷4</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 4</t>
+  </si>
+  <si>
+    <t>Armor_008</t>
+  </si>
+  <si>
+    <t>테스트 갑옷5</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 5</t>
+  </si>
+  <si>
+    <t>Armor_009</t>
+  </si>
+  <si>
+    <t>테스트 갑옷6</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 6</t>
+  </si>
+  <si>
+    <t>Armor_010</t>
+  </si>
+  <si>
+    <t>테스트 갑옷7</t>
+  </si>
+  <si>
+    <t>테스트 갑옷 7</t>
+  </si>
+  <si>
+    <t>Armor_011</t>
+  </si>
+  <si>
+    <t>저항 테스트 갑옷</t>
+  </si>
+  <si>
+    <t>디버프 피해/출혈 저항 연결 테스트용 갑옷</t>
+  </si>
+  <si>
+    <t>Item_ID</t>
+  </si>
+  <si>
+    <t>Item_NAME</t>
+  </si>
+  <si>
+    <t>Item_Option1</t>
+  </si>
+  <si>
+    <t>Item_Option2</t>
+  </si>
+  <si>
+    <t>Item_Description</t>
+  </si>
+  <si>
+    <t>Item_001</t>
+  </si>
+  <si>
+    <t>빨간 포션</t>
+  </si>
+  <si>
+    <t>아이템 설명입니다</t>
+  </si>
+  <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <t>Item_002</t>
+  </si>
+  <si>
+    <t>삽</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Item_003</t>
+  </si>
+  <si>
+    <t>곡괭이</t>
+  </si>
+  <si>
+    <t>Item_004</t>
+  </si>
+  <si>
+    <t>나무사다리</t>
+  </si>
+  <si>
+    <t>Item_005</t>
+  </si>
+  <si>
+    <t>쓰레기</t>
+  </si>
+  <si>
+    <t>Item_006</t>
+  </si>
+  <si>
+    <t>도로롱인형</t>
+  </si>
+  <si>
+    <t>귀엽다!</t>
+  </si>
+  <si>
+    <t>Item_007</t>
+  </si>
+  <si>
+    <t>테스트1</t>
+  </si>
+  <si>
+    <t>Item_008</t>
+  </si>
+  <si>
+    <t>테스트2</t>
+  </si>
+  <si>
+    <t>Item_009</t>
+  </si>
+  <si>
+    <t>테스트3</t>
+  </si>
+  <si>
+    <t>Item_010</t>
+  </si>
+  <si>
+    <t>테스트4</t>
+  </si>
+  <si>
+    <t>Item_011</t>
+  </si>
+  <si>
+    <t>테스트5</t>
+  </si>
+  <si>
+    <t>Item_012</t>
+  </si>
+  <si>
+    <t>테스트6</t>
+  </si>
+  <si>
+    <t>Item_013</t>
+  </si>
+  <si>
+    <t>테스트7</t>
+  </si>
+  <si>
+    <t>Item_014</t>
+  </si>
+  <si>
+    <t>테스트8</t>
+  </si>
+  <si>
+    <t>Item_015</t>
+  </si>
+  <si>
+    <t>테스트9</t>
+  </si>
+  <si>
+    <t>Item_016</t>
+  </si>
+  <si>
+    <t>테스트10</t>
+  </si>
+  <si>
+    <t>Item_017</t>
+  </si>
+  <si>
+    <t>테스트11</t>
+  </si>
+  <si>
+    <t>Item_018</t>
+  </si>
+  <si>
+    <t>테스트12</t>
+  </si>
+  <si>
+    <t>Item_019</t>
+  </si>
+  <si>
+    <t>테스트13</t>
+  </si>
+  <si>
+    <t>Item_020</t>
+  </si>
+  <si>
+    <t>테스트14</t>
+  </si>
+  <si>
+    <t>Option_Description</t>
+  </si>
+  <si>
+    <t>Effect_ID</t>
+  </si>
+  <si>
+    <t>Option_Type</t>
+  </si>
+  <si>
+    <t>추가 공격력</t>
+  </si>
+  <si>
+    <t>Effect_001</t>
+  </si>
+  <si>
+    <t>크리티컬 확률 증가</t>
+  </si>
+  <si>
+    <t>Effect_002</t>
+  </si>
+  <si>
+    <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
+  </si>
+  <si>
+    <t>Effect_003</t>
+  </si>
+  <si>
+    <t>최대 체력 비례 회복</t>
+  </si>
+  <si>
+    <t>Effect_004</t>
+  </si>
+  <si>
+    <t>공격 속도 증가</t>
+  </si>
+  <si>
+    <t>Effect_005</t>
+  </si>
+  <si>
+    <t>체력을 회복합니다</t>
+  </si>
+  <si>
+    <t>Effect_006</t>
+  </si>
+  <si>
+    <t>정신력을 회복합니다</t>
+  </si>
+  <si>
+    <t>Effect_007</t>
+  </si>
+  <si>
+    <t>적중 시 대상의 다음 공격 1회 실패</t>
+  </si>
+  <si>
+    <t>Effect_008</t>
+  </si>
+  <si>
+    <t>출혈: 공격 시 스택 기반 확률로 최대 체력 비례 고정 피해</t>
+  </si>
+  <si>
+    <t>Effect_009</t>
+  </si>
+  <si>
+    <t>중독: 공격 시 스택 기반 확률로 최대 체력 비례 피해</t>
+  </si>
+  <si>
+    <t>Effect_010</t>
+  </si>
+  <si>
+    <t>신성: 공격 시 적 명중률 감소 및 자기 디버프 정화</t>
+  </si>
+  <si>
+    <t>Effect_011</t>
+  </si>
+  <si>
+    <t>재생: 공격 시 스택 기반 확률로 최대 체력 비례 회복</t>
+  </si>
+  <si>
+    <t>Effect_012</t>
+  </si>
+  <si>
+    <t>빙결: 행동 전 확률로 행동 불가 및 속도 감소</t>
+  </si>
+  <si>
+    <t>Effect_013</t>
+  </si>
+  <si>
+    <t>디버프 피해 저항</t>
+  </si>
+  <si>
+    <t>Effect_014</t>
+  </si>
+  <si>
+    <t>출혈 저항</t>
+  </si>
+  <si>
+    <t>중독 저항</t>
+  </si>
+  <si>
+    <t>빙결 저항</t>
+  </si>
+  <si>
+    <t>광폭화: 전투 시작 시 자신에게 광폭화 부여. 공격 속도 50% 증가, 매 공격 시 최대 체력 1% 반동 피해, 받는 피해 증가, 방어력 -5</t>
+  </si>
+  <si>
+    <t>Effect_015</t>
+  </si>
+  <si>
+    <t>Option_018</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="129"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Malgun Gothic"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Noto Sans KR"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="굴림"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -157,99 +935,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -450,924 +1169,740 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="12.5703125" customWidth="1" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="17" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="14.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="14" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="14" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="14.85546875" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="14.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="14.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="113" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="16.42578125" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="14.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="8.7109375" customWidth="1" min="18" max="26"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="113" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Weapon_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Weapon_Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Weapon_DMG</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>STR_Scaling</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DEX_Scaling</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>INT_Scaling</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>MAG_Scaling</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DIV_Scaling</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>CHR_Scaling</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Option_1_ID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Option_Value1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Option_2_ID</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Option_Value2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="P1" s="6" t="inlineStr">
-        <is>
-          <t>One-Handed</t>
-        </is>
-      </c>
-      <c r="Q1" s="9" t="inlineStr">
-        <is>
-          <t>Item_Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>낡은 검</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="2">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>1.2</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>낡은 검이다</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_002</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>나무 활</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+    <row r="3" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="2">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
         <v>1.2</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Option_005</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>낡은 단검</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+    <row r="4" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
         <v>1.2</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>낡은 지팡이</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+    <row r="5" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
         <v>1.2</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>화염 검</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+    <row r="6" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="2">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>12</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="2">
         <v>12</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Option_003</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="2">
         <v>5</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
+      <c r="L6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>100</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기1</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
+    <row r="7" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="2">
         <v>11</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>0.1</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="2">
         <v>0.1</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="2">
         <v>0.1</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="2">
         <v>0.1</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="2">
         <v>0.1</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="2">
         <v>0.1</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 1</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
+      <c r="J7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기2</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
+    <row r="8" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="2">
         <v>12</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>0.1</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="2">
         <v>0.1</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="2">
         <v>0.1</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="2">
         <v>0.1</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="2">
         <v>0.1</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="2">
         <v>0.1</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 2</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
+      <c r="J8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기3</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
+    <row r="9" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="2">
         <v>13</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>0.1</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="2">
         <v>0.1</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="2">
         <v>0.1</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="2">
         <v>0.1</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="2">
         <v>0.1</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="2">
         <v>0.1</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 3</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
+      <c r="J9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기4</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
+    <row r="10" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="2">
         <v>14</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>0.1</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="2">
         <v>0.1</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="2">
         <v>0.1</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="2">
         <v>0.1</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="2">
         <v>0.1</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="2">
         <v>0.1</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 4</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
+      <c r="J10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기5</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
+    <row r="11" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="2">
         <v>15</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="2">
         <v>0.1</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="2">
         <v>0.1</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="2">
         <v>0.1</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="2">
         <v>0.1</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="2">
         <v>0.1</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="2">
         <v>0.1</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 5</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
+      <c r="J11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기6</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
+    <row r="12" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="2">
         <v>16</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>0.1</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="2">
         <v>0.1</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="2">
         <v>0.1</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="2">
         <v>0.1</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="2">
         <v>0.1</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="2">
         <v>0.1</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 6</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
+      <c r="J12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>테스트 무기7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
+    <row r="13" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2">
         <v>17</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2">
         <v>0.1</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="2">
         <v>0.1</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="2">
         <v>0.1</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="2">
         <v>0.1</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="2">
         <v>0.1</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="2">
         <v>0.1</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>테스트 무기 7</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
+      <c r="J13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Weapon_013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>화염 검</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
+    <row r="14" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="2">
         <v>18</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>0.1</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="2">
         <v>0.1</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="2">
         <v>0.1</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="2">
         <v>0.1</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="2">
         <v>0.1</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="2">
         <v>0.1</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Option_003</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
+      <c r="J14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="2">
         <v>5</v>
       </c>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>공격 적중 시 화상을 부여하는 테스트 무기</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="2" t="n"/>
+    <row r="15" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A16" s="2"/>
     </row>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
@@ -2354,641 +2889,463 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="12" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="15" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="15" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="13" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="12" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="12" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="26"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col min="1" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="26" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Armor_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Armor_NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Armor_DEF</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Armor_HP</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Armor_Option1</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Option1_Value</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Armor_Option2</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Option2_Value</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Item_Price</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
-      <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
-      <c r="X1" s="3" t="n"/>
-      <c r="Y1" s="3" t="n"/>
-      <c r="Z1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Armor_001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>철 갑옷</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Option_001</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>튼튼한 철로 만든 철 갑옷이다 사용자의 몸을 든든하게 지켜준다</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="G2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Armor_002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>가죽 갑옷</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="3" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Option_002</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
         <v>90</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>단단한 가죽으로 만든 갑옷이다. 사용자의 몸을 지켜준다</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="G3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Armor_003</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>천 갑옷</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>5000</v>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Option_004</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>천으로 만든 갑옷이다</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="G4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Armor_004</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷1</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 1</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="E5" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Armor_005</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷2</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 2</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+      <c r="E6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Armor_006</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷3</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 3</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
+      <c r="E7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Armor_007</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷4</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>4</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 4</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
+      <c r="E8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Armor_008</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row r="9" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>5</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 5</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
+      <c r="E9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Armor_009</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷6</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row r="10" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 6</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
+      <c r="E10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Armor_010</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>테스트 갑옷7</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+    <row r="11" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11">
         <v>7</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>7</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>테스트 갑옷 7</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+      <c r="E11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Armor_011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>저항 테스트 갑옷</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>100</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Option_014</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12">
         <v>20</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Option_015</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12">
         <v>30</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>디버프 피해/출혈 저항 연결 테스트용 갑옷</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
+      <c r="I12" t="s">
+        <v>170</v>
+      </c>
+      <c r="J12" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1"/>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
@@ -3974,630 +4331,443 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="9.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="20.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="12.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="8.7109375" customWidth="1" min="9" max="26"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Item_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Item_NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Item_Option1</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Option1_Value</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Item_Option2</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Option2_Value</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Item_Description</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>ItemType</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Item_Price</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
-      <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
-      <c r="X1" s="3" t="n"/>
-      <c r="Y1" s="3" t="n"/>
-      <c r="Z1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Item_001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>빨간 포션</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Option_006</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+      <c r="E2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Item_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>삽</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+    <row r="3" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Item_003</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>곡괭이</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+    <row r="4" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Item_004</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>나무사다리</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+    <row r="5" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Item_005</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>쓰레기</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+    <row r="6" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Item_006</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>도로롱인형</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Option_007</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>귀엽다!</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="G7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Item_007</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>테스트1</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+    <row r="8" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Item_008</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>테스트2</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+    <row r="9" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Item_009</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>테스트3</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+    <row r="10" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Item_010</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>테스트4</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+    <row r="11" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Item_011</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>테스트5</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+    <row r="12" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Item_012</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>테스트6</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+    <row r="13" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Item_013</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>테스트7</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+    <row r="14" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Item_014</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>테스트8</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+    <row r="15" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15">
         <v>10</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Item_015</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>테스트9</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+    <row r="16" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I16">
         <v>10</v>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Item_016</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>테스트10</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+    <row r="17" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17">
         <v>10</v>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Item_017</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>테스트11</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+    <row r="18" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Item_018</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>테스트12</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+    <row r="19" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Item_019</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>테스트13</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+    <row r="20" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Item_020</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>테스트14</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>아이템 설명입니다</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+    <row r="21" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1"/>
-    <row r="23" ht="16.5" customHeight="1"/>
-    <row r="24" ht="16.5" customHeight="1"/>
-    <row r="25" ht="16.5" customHeight="1"/>
-    <row r="26" ht="16.5" customHeight="1"/>
-    <row r="27" ht="16.5" customHeight="1"/>
-    <row r="28" ht="16.5" customHeight="1"/>
-    <row r="29" ht="16.5" customHeight="1"/>
-    <row r="30" ht="16.5" customHeight="1"/>
-    <row r="31" ht="16.5" customHeight="1"/>
-    <row r="32" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="24" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="25" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="26" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="27" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="28" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="29" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="30" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:9" ht="16.5" customHeight="1"/>
+    <row r="32" spans="1:9" ht="16.5" customHeight="1"/>
     <row r="33" ht="16.5" customHeight="1"/>
     <row r="34" ht="16.5" customHeight="1"/>
     <row r="35" ht="16.5" customHeight="1"/>
@@ -5567,427 +5737,297 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="8.7109375" customWidth="1" min="5" max="26"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="129.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Option_ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option_Description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Effect_ID</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Option_Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16.5" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Option_001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>추가 공격력</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Effect_001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Option_002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>크리티컬 확률 증가</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Effect_002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Option_003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>공격 적중 시 최대 체력 비례 데미지 디버프</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Effect_003</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Option_004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>최대 체력 비례 회복</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Effect_004</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Option_005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>공격 속도 증가</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Effect_005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Option_006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>체력을 회복합니다</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Effect_006</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Option_007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>정신력을 회복합니다</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Effect_007</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Option_008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>적중 시 대상의 다음 공격 1회 실패</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Effect_008</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Option_009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>출혈: 공격 시 스택 기반 확률로 최대 체력 비례 고정 피해</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Effect_009</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Option_010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>중독: 공격 시 스택 기반 확률로 최대 체력 비례 피해</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Effect_010</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Option_011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>신성: 공격 시 적 명중률 감소 및 자기 디버프 정화</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Effect_011</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Option_012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>재생: 공격 시 스택 기반 확률로 최대 체력 비례 회복</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Effect_012</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Option_013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>빙결: 행동 전 확률로 행동 불가 및 속도 감소</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Effect_013</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Option_014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>디버프 피해 저항</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Effect_014</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Option_015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>출혈 저항</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Effect_014</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Option_016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>중독 저항</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Effect_014</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Option_017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>빙결 저항</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Effect_014</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1"/>
-    <row r="20" ht="16.5" customHeight="1"/>
-    <row r="21" ht="16.5" customHeight="1"/>
-    <row r="22" ht="16.5" customHeight="1"/>
-    <row r="23" ht="16.5" customHeight="1"/>
-    <row r="24" ht="16.5" customHeight="1"/>
-    <row r="25" ht="16.5" customHeight="1"/>
-    <row r="26" ht="16.5" customHeight="1"/>
-    <row r="27" ht="16.5" customHeight="1"/>
-    <row r="28" ht="16.5" customHeight="1"/>
-    <row r="29" ht="16.5" customHeight="1"/>
-    <row r="30" ht="16.5" customHeight="1"/>
-    <row r="31" ht="16.5" customHeight="1"/>
-    <row r="32" ht="16.5" customHeight="1"/>
+    <row r="1" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="23" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="24" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="25" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="26" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="27" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="28" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="29" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="30" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:4" ht="16.5" customHeight="1"/>
+    <row r="32" spans="1:4" ht="16.5" customHeight="1"/>
     <row r="33" ht="16.5" customHeight="1"/>
     <row r="34" ht="16.5" customHeight="1"/>
     <row r="35" ht="16.5" customHeight="1"/>
@@ -6957,1123 +6997,907 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Option_ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>StatusType</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ApplyMode</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>StackPolicy</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>MaxStack</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>TickInterval</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>TriggerType</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ValueMode</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>BaseChance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ChancePerStack</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>BaseValue</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ValuePerStack</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>StatType</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ResistanceType</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>MaxRemoveCount</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Option_001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AddDamage</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>OnHit</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Option_002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CriticalChance</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>CritChance</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Option_003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Burn</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TimedTick</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Refresh</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>OnTick</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Option_004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HealOverTime</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TimedTick</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Refresh</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>OnTick</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Option_005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AttackSpeed</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Option_006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OneShotHPHeal</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>OnUse</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Option_007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>OneShotMPHeal</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>OnUse</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Option_008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ForcedMiss</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>OneShotState</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9">
         <v>99</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BeforeAttack</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>StackCount</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Option_009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bleed</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10">
         <v>99</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10">
         <v>7</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>2</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>BleedResist</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Option_010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Poison</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="O10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11">
         <v>99</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11">
         <v>100</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>1</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>PoisonResist</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Option_011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Holy</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="O11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12">
         <v>99</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12">
         <v>7</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>4</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>1</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Option_012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Regen</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13">
         <v>99</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>OnAttack</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PercentMaxHP</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13">
         <v>100</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>1</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Option_013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Stacking</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14">
         <v>10</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>BeforeAttack</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Percent</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14">
         <v>10</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>10</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>5</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>FreezeResist</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Option_014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DebuffDamageResist</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="N14" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>DebuffDamageResist</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Option_015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BleedResist</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>67</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>BleedResist</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Option_016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PoisonResist</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>55</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>PoisonResist</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Option_017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FreezeResist</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ignore</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>58</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>OnEquip</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Flat</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>FreezeResist</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>65</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="P19">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>